--- a/automatizacion/modificaciones.xlsx
+++ b/automatizacion/modificaciones.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modificaciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qué hace cada opción" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qué hace cada opción" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modificaciones'!$A$5:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modificaciones'!$A$5:$Q$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -146,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +177,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -544,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1005"/>
+  <dimension ref="A1:Q1005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -552,17 +554,18 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -608,31 +611,32 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Tablas y condicionales (paso 2)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n"/>
       <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Solo cambio</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Textos</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
-      <c r="N4" s="6" t="n"/>
       <c r="O4" s="6" t="n"/>
       <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -660,57 +664,62 @@
           <t>Delta (vacío: +1 rectificación, −1 cambio)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Cambio: sentido (Beneficioso / Perjudicial)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Campos a modificar</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Lista de campos (separados por ;)</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Agregar una fila a cada tabla</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Pasar «ilimitado» a limitado</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Cambiar canales (TV de paga)</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Cambio: fecha de ejecución</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Texto del sello (vacío: «Rectificación» / «Cambio»)</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>Código SIRT</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>Fecha de ejecución</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>Detalle</t>
         </is>
@@ -727,7 +736,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>TE-IF-CM-004</t>
+          <t>TE-TF-CM-005</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -735,30 +744,31 @@
           <t>Rectificación</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Por defecto</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="n"/>
       <c r="I6" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="11" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="11" t="n"/>
+      <c r="P6" s="11" t="n"/>
+      <c r="Q6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -771,7 +781,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>TE-SMP-CM-003</t>
+          <t>TE-TF-CM-006</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -779,30 +789,35 @@
           <t>Cambio</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Todos los campos</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="H7" s="9" t="n"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr"/>
-      <c r="M7" s="11" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="11" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="11" t="n"/>
+      <c r="O7" s="11" t="n"/>
+      <c r="P7" s="11" t="n"/>
+      <c r="Q7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -815,26 +830,26 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>TE-TVP-CM-005</t>
+          <t>TE-TF-CM-008</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Rectificación</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr">
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Todos los campos</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="H8" s="9" t="n"/>
       <c r="I8" s="8" t="inlineStr">
         <is>
           <t>No</t>
@@ -845,12 +860,13 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="11" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="11" t="n"/>
+      <c r="O8" s="11" t="n"/>
+      <c r="P8" s="11" t="n"/>
+      <c r="Q8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -863,28 +879,24 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>TE-EMP-CM-002</t>
+          <t>TE-TF-CM-009</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Por defecto</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Solo la lista</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Otros datos generales; Valor del servicio</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -892,13 +904,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="9" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="11" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11" t="n"/>
+      <c r="P9" s="11" t="n"/>
+      <c r="Q9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -911,7 +928,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>TE-TF-CM-005</t>
+          <t>TE-TFP-CM-005</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -919,3064 +936,4830 @@
           <t>Rectificación</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Solo la lista</t>
-        </is>
-      </c>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Otros datos generales; Valor del servicio</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n"/>
       <c r="I10" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr"/>
-      <c r="L10" s="9" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="11" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="11" t="n"/>
+      <c r="O10" s="11" t="n"/>
+      <c r="P10" s="11" t="n"/>
+      <c r="Q10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>TL-LYC-CM-001</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-006</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-008</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-008</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Rectificación</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-011</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-012</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-008</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-011</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-012</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-007</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-008</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-010</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-007</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-008</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-010</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-006</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-008</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-009</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-005</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-006</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-008</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-005</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-008</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-009</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-007</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-009</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-010</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-007</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-008</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-009</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-008</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" s="12" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-009</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-010</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-007</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-008</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-009</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-010</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Detalle en hoja Campos</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TE-OS-CM-007</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TE-OS-CM-008</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TE-OS-CM-009</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TE-AC-CM-007</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TE-AC-CM-008</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L51" s="12" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TE-AC-CM-009</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-106</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-107</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-108</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-109</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-111</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-112</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Todos los campos</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L58" s="12" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-102</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>Por defecto</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="9" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="11" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="K12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="K13" s="12" t="n"/>
-    </row>
-    <row r="14">
-      <c r="K14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="K15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="K16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="K18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="K19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="K20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="K21" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="K22" s="12" t="n"/>
-    </row>
-    <row r="23">
-      <c r="K23" s="12" t="n"/>
-    </row>
-    <row r="24">
-      <c r="K24" s="12" t="n"/>
-    </row>
-    <row r="25">
-      <c r="K25" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="K26" s="12" t="n"/>
-    </row>
-    <row r="27">
-      <c r="K27" s="12" t="n"/>
-    </row>
-    <row r="28">
-      <c r="K28" s="12" t="n"/>
-    </row>
-    <row r="29">
-      <c r="K29" s="12" t="n"/>
-    </row>
-    <row r="30">
-      <c r="K30" s="12" t="n"/>
-    </row>
-    <row r="31">
-      <c r="K31" s="12" t="n"/>
-    </row>
-    <row r="32">
-      <c r="K32" s="12" t="n"/>
-    </row>
-    <row r="33">
-      <c r="K33" s="12" t="n"/>
-    </row>
-    <row r="34">
-      <c r="K34" s="12" t="n"/>
-    </row>
-    <row r="35">
-      <c r="K35" s="12" t="n"/>
-    </row>
-    <row r="36">
-      <c r="K36" s="12" t="n"/>
-    </row>
-    <row r="37">
-      <c r="K37" s="12" t="n"/>
-    </row>
-    <row r="38">
-      <c r="K38" s="12" t="n"/>
-    </row>
-    <row r="39">
-      <c r="K39" s="12" t="n"/>
-    </row>
-    <row r="40">
-      <c r="K40" s="12" t="n"/>
-    </row>
-    <row r="41">
-      <c r="K41" s="12" t="n"/>
-    </row>
-    <row r="42">
-      <c r="K42" s="12" t="n"/>
-    </row>
-    <row r="43">
-      <c r="K43" s="12" t="n"/>
-    </row>
-    <row r="44">
-      <c r="K44" s="12" t="n"/>
-    </row>
-    <row r="45">
-      <c r="K45" s="12" t="n"/>
-    </row>
-    <row r="46">
-      <c r="K46" s="12" t="n"/>
-    </row>
-    <row r="47">
-      <c r="K47" s="12" t="n"/>
-    </row>
-    <row r="48">
-      <c r="K48" s="12" t="n"/>
-    </row>
-    <row r="49">
-      <c r="K49" s="12" t="n"/>
-    </row>
-    <row r="50">
-      <c r="K50" s="12" t="n"/>
-    </row>
-    <row r="51">
-      <c r="K51" s="12" t="n"/>
-    </row>
-    <row r="52">
-      <c r="K52" s="12" t="n"/>
-    </row>
-    <row r="53">
-      <c r="K53" s="12" t="n"/>
-    </row>
-    <row r="54">
-      <c r="K54" s="12" t="n"/>
-    </row>
-    <row r="55">
-      <c r="K55" s="12" t="n"/>
-    </row>
-    <row r="56">
-      <c r="K56" s="12" t="n"/>
-    </row>
-    <row r="57">
-      <c r="K57" s="12" t="n"/>
-    </row>
-    <row r="58">
-      <c r="K58" s="12" t="n"/>
-    </row>
-    <row r="59">
-      <c r="K59" s="12" t="n"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="n"/>
     </row>
     <row r="60">
-      <c r="K60" s="12" t="n"/>
+      <c r="A60" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TL-LYC-CM-130</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Rectificación</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Por defecto</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L60" s="12" t="n"/>
     </row>
     <row r="61">
-      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="12" t="n"/>
     </row>
     <row r="62">
-      <c r="K62" s="12" t="n"/>
+      <c r="L62" s="12" t="n"/>
     </row>
     <row r="63">
-      <c r="K63" s="12" t="n"/>
+      <c r="L63" s="12" t="n"/>
     </row>
     <row r="64">
-      <c r="K64" s="12" t="n"/>
+      <c r="L64" s="12" t="n"/>
     </row>
     <row r="65">
-      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="12" t="n"/>
     </row>
     <row r="66">
-      <c r="K66" s="12" t="n"/>
+      <c r="L66" s="12" t="n"/>
     </row>
     <row r="67">
-      <c r="K67" s="12" t="n"/>
+      <c r="L67" s="12" t="n"/>
     </row>
     <row r="68">
-      <c r="K68" s="12" t="n"/>
+      <c r="L68" s="12" t="n"/>
     </row>
     <row r="69">
-      <c r="K69" s="12" t="n"/>
+      <c r="L69" s="12" t="n"/>
     </row>
     <row r="70">
-      <c r="K70" s="12" t="n"/>
+      <c r="L70" s="12" t="n"/>
     </row>
     <row r="71">
-      <c r="K71" s="12" t="n"/>
+      <c r="L71" s="12" t="n"/>
     </row>
     <row r="72">
-      <c r="K72" s="12" t="n"/>
+      <c r="L72" s="12" t="n"/>
     </row>
     <row r="73">
-      <c r="K73" s="12" t="n"/>
+      <c r="L73" s="12" t="n"/>
     </row>
     <row r="74">
-      <c r="K74" s="12" t="n"/>
+      <c r="L74" s="12" t="n"/>
     </row>
     <row r="75">
-      <c r="K75" s="12" t="n"/>
+      <c r="L75" s="12" t="n"/>
     </row>
     <row r="76">
-      <c r="K76" s="12" t="n"/>
+      <c r="L76" s="12" t="n"/>
     </row>
     <row r="77">
-      <c r="K77" s="12" t="n"/>
+      <c r="L77" s="12" t="n"/>
     </row>
     <row r="78">
-      <c r="K78" s="12" t="n"/>
+      <c r="L78" s="12" t="n"/>
     </row>
     <row r="79">
-      <c r="K79" s="12" t="n"/>
+      <c r="L79" s="12" t="n"/>
     </row>
     <row r="80">
-      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="12" t="n"/>
     </row>
     <row r="81">
-      <c r="K81" s="12" t="n"/>
+      <c r="L81" s="12" t="n"/>
     </row>
     <row r="82">
-      <c r="K82" s="12" t="n"/>
+      <c r="L82" s="12" t="n"/>
     </row>
     <row r="83">
-      <c r="K83" s="12" t="n"/>
+      <c r="L83" s="12" t="n"/>
     </row>
     <row r="84">
-      <c r="K84" s="12" t="n"/>
+      <c r="L84" s="12" t="n"/>
     </row>
     <row r="85">
-      <c r="K85" s="12" t="n"/>
+      <c r="L85" s="12" t="n"/>
     </row>
     <row r="86">
-      <c r="K86" s="12" t="n"/>
+      <c r="L86" s="12" t="n"/>
     </row>
     <row r="87">
-      <c r="K87" s="12" t="n"/>
+      <c r="L87" s="12" t="n"/>
     </row>
     <row r="88">
-      <c r="K88" s="12" t="n"/>
+      <c r="L88" s="12" t="n"/>
     </row>
     <row r="89">
-      <c r="K89" s="12" t="n"/>
+      <c r="L89" s="12" t="n"/>
     </row>
     <row r="90">
-      <c r="K90" s="12" t="n"/>
+      <c r="L90" s="12" t="n"/>
     </row>
     <row r="91">
-      <c r="K91" s="12" t="n"/>
+      <c r="L91" s="12" t="n"/>
     </row>
     <row r="92">
-      <c r="K92" s="12" t="n"/>
+      <c r="L92" s="12" t="n"/>
     </row>
     <row r="93">
-      <c r="K93" s="12" t="n"/>
+      <c r="L93" s="12" t="n"/>
     </row>
     <row r="94">
-      <c r="K94" s="12" t="n"/>
+      <c r="L94" s="12" t="n"/>
     </row>
     <row r="95">
-      <c r="K95" s="12" t="n"/>
+      <c r="L95" s="12" t="n"/>
     </row>
     <row r="96">
-      <c r="K96" s="12" t="n"/>
+      <c r="L96" s="12" t="n"/>
     </row>
     <row r="97">
-      <c r="K97" s="12" t="n"/>
+      <c r="L97" s="12" t="n"/>
     </row>
     <row r="98">
-      <c r="K98" s="12" t="n"/>
+      <c r="L98" s="12" t="n"/>
     </row>
     <row r="99">
-      <c r="K99" s="12" t="n"/>
+      <c r="L99" s="12" t="n"/>
     </row>
     <row r="100">
-      <c r="K100" s="12" t="n"/>
+      <c r="L100" s="12" t="n"/>
     </row>
     <row r="101">
-      <c r="K101" s="12" t="n"/>
+      <c r="L101" s="12" t="n"/>
     </row>
     <row r="102">
-      <c r="K102" s="12" t="n"/>
+      <c r="L102" s="12" t="n"/>
     </row>
     <row r="103">
-      <c r="K103" s="12" t="n"/>
+      <c r="L103" s="12" t="n"/>
     </row>
     <row r="104">
-      <c r="K104" s="12" t="n"/>
+      <c r="L104" s="12" t="n"/>
     </row>
     <row r="105">
-      <c r="K105" s="12" t="n"/>
+      <c r="L105" s="12" t="n"/>
     </row>
     <row r="106">
-      <c r="K106" s="12" t="n"/>
+      <c r="L106" s="12" t="n"/>
     </row>
     <row r="107">
-      <c r="K107" s="12" t="n"/>
+      <c r="L107" s="12" t="n"/>
     </row>
     <row r="108">
-      <c r="K108" s="12" t="n"/>
+      <c r="L108" s="12" t="n"/>
     </row>
     <row r="109">
-      <c r="K109" s="12" t="n"/>
+      <c r="L109" s="12" t="n"/>
     </row>
     <row r="110">
-      <c r="K110" s="12" t="n"/>
+      <c r="L110" s="12" t="n"/>
     </row>
     <row r="111">
-      <c r="K111" s="12" t="n"/>
+      <c r="L111" s="12" t="n"/>
     </row>
     <row r="112">
-      <c r="K112" s="12" t="n"/>
+      <c r="L112" s="12" t="n"/>
     </row>
     <row r="113">
-      <c r="K113" s="12" t="n"/>
+      <c r="L113" s="12" t="n"/>
     </row>
     <row r="114">
-      <c r="K114" s="12" t="n"/>
+      <c r="L114" s="12" t="n"/>
     </row>
     <row r="115">
-      <c r="K115" s="12" t="n"/>
+      <c r="L115" s="12" t="n"/>
     </row>
     <row r="116">
-      <c r="K116" s="12" t="n"/>
+      <c r="L116" s="12" t="n"/>
     </row>
     <row r="117">
-      <c r="K117" s="12" t="n"/>
+      <c r="L117" s="12" t="n"/>
     </row>
     <row r="118">
-      <c r="K118" s="12" t="n"/>
+      <c r="L118" s="12" t="n"/>
     </row>
     <row r="119">
-      <c r="K119" s="12" t="n"/>
+      <c r="L119" s="12" t="n"/>
     </row>
     <row r="120">
-      <c r="K120" s="12" t="n"/>
+      <c r="L120" s="12" t="n"/>
     </row>
     <row r="121">
-      <c r="K121" s="12" t="n"/>
+      <c r="L121" s="12" t="n"/>
     </row>
     <row r="122">
-      <c r="K122" s="12" t="n"/>
+      <c r="L122" s="12" t="n"/>
     </row>
     <row r="123">
-      <c r="K123" s="12" t="n"/>
+      <c r="L123" s="12" t="n"/>
     </row>
     <row r="124">
-      <c r="K124" s="12" t="n"/>
+      <c r="L124" s="12" t="n"/>
     </row>
     <row r="125">
-      <c r="K125" s="12" t="n"/>
+      <c r="L125" s="12" t="n"/>
     </row>
     <row r="126">
-      <c r="K126" s="12" t="n"/>
+      <c r="L126" s="12" t="n"/>
     </row>
     <row r="127">
-      <c r="K127" s="12" t="n"/>
+      <c r="L127" s="12" t="n"/>
     </row>
     <row r="128">
-      <c r="K128" s="12" t="n"/>
+      <c r="L128" s="12" t="n"/>
     </row>
     <row r="129">
-      <c r="K129" s="12" t="n"/>
+      <c r="L129" s="12" t="n"/>
     </row>
     <row r="130">
-      <c r="K130" s="12" t="n"/>
+      <c r="L130" s="12" t="n"/>
     </row>
     <row r="131">
-      <c r="K131" s="12" t="n"/>
+      <c r="L131" s="12" t="n"/>
     </row>
     <row r="132">
-      <c r="K132" s="12" t="n"/>
+      <c r="L132" s="12" t="n"/>
     </row>
     <row r="133">
-      <c r="K133" s="12" t="n"/>
+      <c r="L133" s="12" t="n"/>
     </row>
     <row r="134">
-      <c r="K134" s="12" t="n"/>
+      <c r="L134" s="12" t="n"/>
     </row>
     <row r="135">
-      <c r="K135" s="12" t="n"/>
+      <c r="L135" s="12" t="n"/>
     </row>
     <row r="136">
-      <c r="K136" s="12" t="n"/>
+      <c r="L136" s="12" t="n"/>
     </row>
     <row r="137">
-      <c r="K137" s="12" t="n"/>
+      <c r="L137" s="12" t="n"/>
     </row>
     <row r="138">
-      <c r="K138" s="12" t="n"/>
+      <c r="L138" s="12" t="n"/>
     </row>
     <row r="139">
-      <c r="K139" s="12" t="n"/>
+      <c r="L139" s="12" t="n"/>
     </row>
     <row r="140">
-      <c r="K140" s="12" t="n"/>
+      <c r="L140" s="12" t="n"/>
     </row>
     <row r="141">
-      <c r="K141" s="12" t="n"/>
+      <c r="L141" s="12" t="n"/>
     </row>
     <row r="142">
-      <c r="K142" s="12" t="n"/>
+      <c r="L142" s="12" t="n"/>
     </row>
     <row r="143">
-      <c r="K143" s="12" t="n"/>
+      <c r="L143" s="12" t="n"/>
     </row>
     <row r="144">
-      <c r="K144" s="12" t="n"/>
+      <c r="L144" s="12" t="n"/>
     </row>
     <row r="145">
-      <c r="K145" s="12" t="n"/>
+      <c r="L145" s="12" t="n"/>
     </row>
     <row r="146">
-      <c r="K146" s="12" t="n"/>
+      <c r="L146" s="12" t="n"/>
     </row>
     <row r="147">
-      <c r="K147" s="12" t="n"/>
+      <c r="L147" s="12" t="n"/>
     </row>
     <row r="148">
-      <c r="K148" s="12" t="n"/>
+      <c r="L148" s="12" t="n"/>
     </row>
     <row r="149">
-      <c r="K149" s="12" t="n"/>
+      <c r="L149" s="12" t="n"/>
     </row>
     <row r="150">
-      <c r="K150" s="12" t="n"/>
+      <c r="L150" s="12" t="n"/>
     </row>
     <row r="151">
-      <c r="K151" s="12" t="n"/>
+      <c r="L151" s="12" t="n"/>
     </row>
     <row r="152">
-      <c r="K152" s="12" t="n"/>
+      <c r="L152" s="12" t="n"/>
     </row>
     <row r="153">
-      <c r="K153" s="12" t="n"/>
+      <c r="L153" s="12" t="n"/>
     </row>
     <row r="154">
-      <c r="K154" s="12" t="n"/>
+      <c r="L154" s="12" t="n"/>
     </row>
     <row r="155">
-      <c r="K155" s="12" t="n"/>
+      <c r="L155" s="12" t="n"/>
     </row>
     <row r="156">
-      <c r="K156" s="12" t="n"/>
+      <c r="L156" s="12" t="n"/>
     </row>
     <row r="157">
-      <c r="K157" s="12" t="n"/>
+      <c r="L157" s="12" t="n"/>
     </row>
     <row r="158">
-      <c r="K158" s="12" t="n"/>
+      <c r="L158" s="12" t="n"/>
     </row>
     <row r="159">
-      <c r="K159" s="12" t="n"/>
+      <c r="L159" s="12" t="n"/>
     </row>
     <row r="160">
-      <c r="K160" s="12" t="n"/>
+      <c r="L160" s="12" t="n"/>
     </row>
     <row r="161">
-      <c r="K161" s="12" t="n"/>
+      <c r="L161" s="12" t="n"/>
     </row>
     <row r="162">
-      <c r="K162" s="12" t="n"/>
+      <c r="L162" s="12" t="n"/>
     </row>
     <row r="163">
-      <c r="K163" s="12" t="n"/>
+      <c r="L163" s="12" t="n"/>
     </row>
     <row r="164">
-      <c r="K164" s="12" t="n"/>
+      <c r="L164" s="12" t="n"/>
     </row>
     <row r="165">
-      <c r="K165" s="12" t="n"/>
+      <c r="L165" s="12" t="n"/>
     </row>
     <row r="166">
-      <c r="K166" s="12" t="n"/>
+      <c r="L166" s="12" t="n"/>
     </row>
     <row r="167">
-      <c r="K167" s="12" t="n"/>
+      <c r="L167" s="12" t="n"/>
     </row>
     <row r="168">
-      <c r="K168" s="12" t="n"/>
+      <c r="L168" s="12" t="n"/>
     </row>
     <row r="169">
-      <c r="K169" s="12" t="n"/>
+      <c r="L169" s="12" t="n"/>
     </row>
     <row r="170">
-      <c r="K170" s="12" t="n"/>
+      <c r="L170" s="12" t="n"/>
     </row>
     <row r="171">
-      <c r="K171" s="12" t="n"/>
+      <c r="L171" s="12" t="n"/>
     </row>
     <row r="172">
-      <c r="K172" s="12" t="n"/>
+      <c r="L172" s="12" t="n"/>
     </row>
     <row r="173">
-      <c r="K173" s="12" t="n"/>
+      <c r="L173" s="12" t="n"/>
     </row>
     <row r="174">
-      <c r="K174" s="12" t="n"/>
+      <c r="L174" s="12" t="n"/>
     </row>
     <row r="175">
-      <c r="K175" s="12" t="n"/>
+      <c r="L175" s="12" t="n"/>
     </row>
     <row r="176">
-      <c r="K176" s="12" t="n"/>
+      <c r="L176" s="12" t="n"/>
     </row>
     <row r="177">
-      <c r="K177" s="12" t="n"/>
+      <c r="L177" s="12" t="n"/>
     </row>
     <row r="178">
-      <c r="K178" s="12" t="n"/>
+      <c r="L178" s="12" t="n"/>
     </row>
     <row r="179">
-      <c r="K179" s="12" t="n"/>
+      <c r="L179" s="12" t="n"/>
     </row>
     <row r="180">
-      <c r="K180" s="12" t="n"/>
+      <c r="L180" s="12" t="n"/>
     </row>
     <row r="181">
-      <c r="K181" s="12" t="n"/>
+      <c r="L181" s="12" t="n"/>
     </row>
     <row r="182">
-      <c r="K182" s="12" t="n"/>
+      <c r="L182" s="12" t="n"/>
     </row>
     <row r="183">
-      <c r="K183" s="12" t="n"/>
+      <c r="L183" s="12" t="n"/>
     </row>
     <row r="184">
-      <c r="K184" s="12" t="n"/>
+      <c r="L184" s="12" t="n"/>
     </row>
     <row r="185">
-      <c r="K185" s="12" t="n"/>
+      <c r="L185" s="12" t="n"/>
     </row>
     <row r="186">
-      <c r="K186" s="12" t="n"/>
+      <c r="L186" s="12" t="n"/>
     </row>
     <row r="187">
-      <c r="K187" s="12" t="n"/>
+      <c r="L187" s="12" t="n"/>
     </row>
     <row r="188">
-      <c r="K188" s="12" t="n"/>
+      <c r="L188" s="12" t="n"/>
     </row>
     <row r="189">
-      <c r="K189" s="12" t="n"/>
+      <c r="L189" s="12" t="n"/>
     </row>
     <row r="190">
-      <c r="K190" s="12" t="n"/>
+      <c r="L190" s="12" t="n"/>
     </row>
     <row r="191">
-      <c r="K191" s="12" t="n"/>
+      <c r="L191" s="12" t="n"/>
     </row>
     <row r="192">
-      <c r="K192" s="12" t="n"/>
+      <c r="L192" s="12" t="n"/>
     </row>
     <row r="193">
-      <c r="K193" s="12" t="n"/>
+      <c r="L193" s="12" t="n"/>
     </row>
     <row r="194">
-      <c r="K194" s="12" t="n"/>
+      <c r="L194" s="12" t="n"/>
     </row>
     <row r="195">
-      <c r="K195" s="12" t="n"/>
+      <c r="L195" s="12" t="n"/>
     </row>
     <row r="196">
-      <c r="K196" s="12" t="n"/>
+      <c r="L196" s="12" t="n"/>
     </row>
     <row r="197">
-      <c r="K197" s="12" t="n"/>
+      <c r="L197" s="12" t="n"/>
     </row>
     <row r="198">
-      <c r="K198" s="12" t="n"/>
+      <c r="L198" s="12" t="n"/>
     </row>
     <row r="199">
-      <c r="K199" s="12" t="n"/>
+      <c r="L199" s="12" t="n"/>
     </row>
     <row r="200">
-      <c r="K200" s="12" t="n"/>
+      <c r="L200" s="12" t="n"/>
     </row>
     <row r="201">
-      <c r="K201" s="12" t="n"/>
+      <c r="L201" s="12" t="n"/>
     </row>
     <row r="202">
-      <c r="K202" s="12" t="n"/>
+      <c r="L202" s="12" t="n"/>
     </row>
     <row r="203">
-      <c r="K203" s="12" t="n"/>
+      <c r="L203" s="12" t="n"/>
     </row>
     <row r="204">
-      <c r="K204" s="12" t="n"/>
+      <c r="L204" s="12" t="n"/>
     </row>
     <row r="205">
-      <c r="K205" s="12" t="n"/>
+      <c r="L205" s="12" t="n"/>
     </row>
     <row r="206">
-      <c r="K206" s="12" t="n"/>
+      <c r="L206" s="12" t="n"/>
     </row>
     <row r="207">
-      <c r="K207" s="12" t="n"/>
+      <c r="L207" s="12" t="n"/>
     </row>
     <row r="208">
-      <c r="K208" s="12" t="n"/>
+      <c r="L208" s="12" t="n"/>
     </row>
     <row r="209">
-      <c r="K209" s="12" t="n"/>
+      <c r="L209" s="12" t="n"/>
     </row>
     <row r="210">
-      <c r="K210" s="12" t="n"/>
+      <c r="L210" s="12" t="n"/>
     </row>
     <row r="211">
-      <c r="K211" s="12" t="n"/>
+      <c r="L211" s="12" t="n"/>
     </row>
     <row r="212">
-      <c r="K212" s="12" t="n"/>
+      <c r="L212" s="12" t="n"/>
     </row>
     <row r="213">
-      <c r="K213" s="12" t="n"/>
+      <c r="L213" s="12" t="n"/>
     </row>
     <row r="214">
-      <c r="K214" s="12" t="n"/>
+      <c r="L214" s="12" t="n"/>
     </row>
     <row r="215">
-      <c r="K215" s="12" t="n"/>
+      <c r="L215" s="12" t="n"/>
     </row>
     <row r="216">
-      <c r="K216" s="12" t="n"/>
+      <c r="L216" s="12" t="n"/>
     </row>
     <row r="217">
-      <c r="K217" s="12" t="n"/>
+      <c r="L217" s="12" t="n"/>
     </row>
     <row r="218">
-      <c r="K218" s="12" t="n"/>
+      <c r="L218" s="12" t="n"/>
     </row>
     <row r="219">
-      <c r="K219" s="12" t="n"/>
+      <c r="L219" s="12" t="n"/>
     </row>
     <row r="220">
-      <c r="K220" s="12" t="n"/>
+      <c r="L220" s="12" t="n"/>
     </row>
     <row r="221">
-      <c r="K221" s="12" t="n"/>
+      <c r="L221" s="12" t="n"/>
     </row>
     <row r="222">
-      <c r="K222" s="12" t="n"/>
+      <c r="L222" s="12" t="n"/>
     </row>
     <row r="223">
-      <c r="K223" s="12" t="n"/>
+      <c r="L223" s="12" t="n"/>
     </row>
     <row r="224">
-      <c r="K224" s="12" t="n"/>
+      <c r="L224" s="12" t="n"/>
     </row>
     <row r="225">
-      <c r="K225" s="12" t="n"/>
+      <c r="L225" s="12" t="n"/>
     </row>
     <row r="226">
-      <c r="K226" s="12" t="n"/>
+      <c r="L226" s="12" t="n"/>
     </row>
     <row r="227">
-      <c r="K227" s="12" t="n"/>
+      <c r="L227" s="12" t="n"/>
     </row>
     <row r="228">
-      <c r="K228" s="12" t="n"/>
+      <c r="L228" s="12" t="n"/>
     </row>
     <row r="229">
-      <c r="K229" s="12" t="n"/>
+      <c r="L229" s="12" t="n"/>
     </row>
     <row r="230">
-      <c r="K230" s="12" t="n"/>
+      <c r="L230" s="12" t="n"/>
     </row>
     <row r="231">
-      <c r="K231" s="12" t="n"/>
+      <c r="L231" s="12" t="n"/>
     </row>
     <row r="232">
-      <c r="K232" s="12" t="n"/>
+      <c r="L232" s="12" t="n"/>
     </row>
     <row r="233">
-      <c r="K233" s="12" t="n"/>
+      <c r="L233" s="12" t="n"/>
     </row>
     <row r="234">
-      <c r="K234" s="12" t="n"/>
+      <c r="L234" s="12" t="n"/>
     </row>
     <row r="235">
-      <c r="K235" s="12" t="n"/>
+      <c r="L235" s="12" t="n"/>
     </row>
     <row r="236">
-      <c r="K236" s="12" t="n"/>
+      <c r="L236" s="12" t="n"/>
     </row>
     <row r="237">
-      <c r="K237" s="12" t="n"/>
+      <c r="L237" s="12" t="n"/>
     </row>
     <row r="238">
-      <c r="K238" s="12" t="n"/>
+      <c r="L238" s="12" t="n"/>
     </row>
     <row r="239">
-      <c r="K239" s="12" t="n"/>
+      <c r="L239" s="12" t="n"/>
     </row>
     <row r="240">
-      <c r="K240" s="12" t="n"/>
+      <c r="L240" s="12" t="n"/>
     </row>
     <row r="241">
-      <c r="K241" s="12" t="n"/>
+      <c r="L241" s="12" t="n"/>
     </row>
     <row r="242">
-      <c r="K242" s="12" t="n"/>
+      <c r="L242" s="12" t="n"/>
     </row>
     <row r="243">
-      <c r="K243" s="12" t="n"/>
+      <c r="L243" s="12" t="n"/>
     </row>
     <row r="244">
-      <c r="K244" s="12" t="n"/>
+      <c r="L244" s="12" t="n"/>
     </row>
     <row r="245">
-      <c r="K245" s="12" t="n"/>
+      <c r="L245" s="12" t="n"/>
     </row>
     <row r="246">
-      <c r="K246" s="12" t="n"/>
+      <c r="L246" s="12" t="n"/>
     </row>
     <row r="247">
-      <c r="K247" s="12" t="n"/>
+      <c r="L247" s="12" t="n"/>
     </row>
     <row r="248">
-      <c r="K248" s="12" t="n"/>
+      <c r="L248" s="12" t="n"/>
     </row>
     <row r="249">
-      <c r="K249" s="12" t="n"/>
+      <c r="L249" s="12" t="n"/>
     </row>
     <row r="250">
-      <c r="K250" s="12" t="n"/>
+      <c r="L250" s="12" t="n"/>
     </row>
     <row r="251">
-      <c r="K251" s="12" t="n"/>
+      <c r="L251" s="12" t="n"/>
     </row>
     <row r="252">
-      <c r="K252" s="12" t="n"/>
+      <c r="L252" s="12" t="n"/>
     </row>
     <row r="253">
-      <c r="K253" s="12" t="n"/>
+      <c r="L253" s="12" t="n"/>
     </row>
     <row r="254">
-      <c r="K254" s="12" t="n"/>
+      <c r="L254" s="12" t="n"/>
     </row>
     <row r="255">
-      <c r="K255" s="12" t="n"/>
+      <c r="L255" s="12" t="n"/>
     </row>
     <row r="256">
-      <c r="K256" s="12" t="n"/>
+      <c r="L256" s="12" t="n"/>
     </row>
     <row r="257">
-      <c r="K257" s="12" t="n"/>
+      <c r="L257" s="12" t="n"/>
     </row>
     <row r="258">
-      <c r="K258" s="12" t="n"/>
+      <c r="L258" s="12" t="n"/>
     </row>
     <row r="259">
-      <c r="K259" s="12" t="n"/>
+      <c r="L259" s="12" t="n"/>
     </row>
     <row r="260">
-      <c r="K260" s="12" t="n"/>
+      <c r="L260" s="12" t="n"/>
     </row>
     <row r="261">
-      <c r="K261" s="12" t="n"/>
+      <c r="L261" s="12" t="n"/>
     </row>
     <row r="262">
-      <c r="K262" s="12" t="n"/>
+      <c r="L262" s="12" t="n"/>
     </row>
     <row r="263">
-      <c r="K263" s="12" t="n"/>
+      <c r="L263" s="12" t="n"/>
     </row>
     <row r="264">
-      <c r="K264" s="12" t="n"/>
+      <c r="L264" s="12" t="n"/>
     </row>
     <row r="265">
-      <c r="K265" s="12" t="n"/>
+      <c r="L265" s="12" t="n"/>
     </row>
     <row r="266">
-      <c r="K266" s="12" t="n"/>
+      <c r="L266" s="12" t="n"/>
     </row>
     <row r="267">
-      <c r="K267" s="12" t="n"/>
+      <c r="L267" s="12" t="n"/>
     </row>
     <row r="268">
-      <c r="K268" s="12" t="n"/>
+      <c r="L268" s="12" t="n"/>
     </row>
     <row r="269">
-      <c r="K269" s="12" t="n"/>
+      <c r="L269" s="12" t="n"/>
     </row>
     <row r="270">
-      <c r="K270" s="12" t="n"/>
+      <c r="L270" s="12" t="n"/>
     </row>
     <row r="271">
-      <c r="K271" s="12" t="n"/>
+      <c r="L271" s="12" t="n"/>
     </row>
     <row r="272">
-      <c r="K272" s="12" t="n"/>
+      <c r="L272" s="12" t="n"/>
     </row>
     <row r="273">
-      <c r="K273" s="12" t="n"/>
+      <c r="L273" s="12" t="n"/>
     </row>
     <row r="274">
-      <c r="K274" s="12" t="n"/>
+      <c r="L274" s="12" t="n"/>
     </row>
     <row r="275">
-      <c r="K275" s="12" t="n"/>
+      <c r="L275" s="12" t="n"/>
     </row>
     <row r="276">
-      <c r="K276" s="12" t="n"/>
+      <c r="L276" s="12" t="n"/>
     </row>
     <row r="277">
-      <c r="K277" s="12" t="n"/>
+      <c r="L277" s="12" t="n"/>
     </row>
     <row r="278">
-      <c r="K278" s="12" t="n"/>
+      <c r="L278" s="12" t="n"/>
     </row>
     <row r="279">
-      <c r="K279" s="12" t="n"/>
+      <c r="L279" s="12" t="n"/>
     </row>
     <row r="280">
-      <c r="K280" s="12" t="n"/>
+      <c r="L280" s="12" t="n"/>
     </row>
     <row r="281">
-      <c r="K281" s="12" t="n"/>
+      <c r="L281" s="12" t="n"/>
     </row>
     <row r="282">
-      <c r="K282" s="12" t="n"/>
+      <c r="L282" s="12" t="n"/>
     </row>
     <row r="283">
-      <c r="K283" s="12" t="n"/>
+      <c r="L283" s="12" t="n"/>
     </row>
     <row r="284">
-      <c r="K284" s="12" t="n"/>
+      <c r="L284" s="12" t="n"/>
     </row>
     <row r="285">
-      <c r="K285" s="12" t="n"/>
+      <c r="L285" s="12" t="n"/>
     </row>
     <row r="286">
-      <c r="K286" s="12" t="n"/>
+      <c r="L286" s="12" t="n"/>
     </row>
     <row r="287">
-      <c r="K287" s="12" t="n"/>
+      <c r="L287" s="12" t="n"/>
     </row>
     <row r="288">
-      <c r="K288" s="12" t="n"/>
+      <c r="L288" s="12" t="n"/>
     </row>
     <row r="289">
-      <c r="K289" s="12" t="n"/>
+      <c r="L289" s="12" t="n"/>
     </row>
     <row r="290">
-      <c r="K290" s="12" t="n"/>
+      <c r="L290" s="12" t="n"/>
     </row>
     <row r="291">
-      <c r="K291" s="12" t="n"/>
+      <c r="L291" s="12" t="n"/>
     </row>
     <row r="292">
-      <c r="K292" s="12" t="n"/>
+      <c r="L292" s="12" t="n"/>
     </row>
     <row r="293">
-      <c r="K293" s="12" t="n"/>
+      <c r="L293" s="12" t="n"/>
     </row>
     <row r="294">
-      <c r="K294" s="12" t="n"/>
+      <c r="L294" s="12" t="n"/>
     </row>
     <row r="295">
-      <c r="K295" s="12" t="n"/>
+      <c r="L295" s="12" t="n"/>
     </row>
     <row r="296">
-      <c r="K296" s="12" t="n"/>
+      <c r="L296" s="12" t="n"/>
     </row>
     <row r="297">
-      <c r="K297" s="12" t="n"/>
+      <c r="L297" s="12" t="n"/>
     </row>
     <row r="298">
-      <c r="K298" s="12" t="n"/>
+      <c r="L298" s="12" t="n"/>
     </row>
     <row r="299">
-      <c r="K299" s="12" t="n"/>
+      <c r="L299" s="12" t="n"/>
     </row>
     <row r="300">
-      <c r="K300" s="12" t="n"/>
+      <c r="L300" s="12" t="n"/>
     </row>
     <row r="301">
-      <c r="K301" s="12" t="n"/>
+      <c r="L301" s="12" t="n"/>
     </row>
     <row r="302">
-      <c r="K302" s="12" t="n"/>
+      <c r="L302" s="12" t="n"/>
     </row>
     <row r="303">
-      <c r="K303" s="12" t="n"/>
+      <c r="L303" s="12" t="n"/>
     </row>
     <row r="304">
-      <c r="K304" s="12" t="n"/>
+      <c r="L304" s="12" t="n"/>
     </row>
     <row r="305">
-      <c r="K305" s="12" t="n"/>
+      <c r="L305" s="12" t="n"/>
     </row>
     <row r="306">
-      <c r="K306" s="12" t="n"/>
+      <c r="L306" s="12" t="n"/>
     </row>
     <row r="307">
-      <c r="K307" s="12" t="n"/>
+      <c r="L307" s="12" t="n"/>
     </row>
     <row r="308">
-      <c r="K308" s="12" t="n"/>
+      <c r="L308" s="12" t="n"/>
     </row>
     <row r="309">
-      <c r="K309" s="12" t="n"/>
+      <c r="L309" s="12" t="n"/>
     </row>
     <row r="310">
-      <c r="K310" s="12" t="n"/>
+      <c r="L310" s="12" t="n"/>
     </row>
     <row r="311">
-      <c r="K311" s="12" t="n"/>
+      <c r="L311" s="12" t="n"/>
     </row>
     <row r="312">
-      <c r="K312" s="12" t="n"/>
+      <c r="L312" s="12" t="n"/>
     </row>
     <row r="313">
-      <c r="K313" s="12" t="n"/>
+      <c r="L313" s="12" t="n"/>
     </row>
     <row r="314">
-      <c r="K314" s="12" t="n"/>
+      <c r="L314" s="12" t="n"/>
     </row>
     <row r="315">
-      <c r="K315" s="12" t="n"/>
+      <c r="L315" s="12" t="n"/>
     </row>
     <row r="316">
-      <c r="K316" s="12" t="n"/>
+      <c r="L316" s="12" t="n"/>
     </row>
     <row r="317">
-      <c r="K317" s="12" t="n"/>
+      <c r="L317" s="12" t="n"/>
     </row>
     <row r="318">
-      <c r="K318" s="12" t="n"/>
+      <c r="L318" s="12" t="n"/>
     </row>
     <row r="319">
-      <c r="K319" s="12" t="n"/>
+      <c r="L319" s="12" t="n"/>
     </row>
     <row r="320">
-      <c r="K320" s="12" t="n"/>
+      <c r="L320" s="12" t="n"/>
     </row>
     <row r="321">
-      <c r="K321" s="12" t="n"/>
+      <c r="L321" s="12" t="n"/>
     </row>
     <row r="322">
-      <c r="K322" s="12" t="n"/>
+      <c r="L322" s="12" t="n"/>
     </row>
     <row r="323">
-      <c r="K323" s="12" t="n"/>
+      <c r="L323" s="12" t="n"/>
     </row>
     <row r="324">
-      <c r="K324" s="12" t="n"/>
+      <c r="L324" s="12" t="n"/>
     </row>
     <row r="325">
-      <c r="K325" s="12" t="n"/>
+      <c r="L325" s="12" t="n"/>
     </row>
     <row r="326">
-      <c r="K326" s="12" t="n"/>
+      <c r="L326" s="12" t="n"/>
     </row>
     <row r="327">
-      <c r="K327" s="12" t="n"/>
+      <c r="L327" s="12" t="n"/>
     </row>
     <row r="328">
-      <c r="K328" s="12" t="n"/>
+      <c r="L328" s="12" t="n"/>
     </row>
     <row r="329">
-      <c r="K329" s="12" t="n"/>
+      <c r="L329" s="12" t="n"/>
     </row>
     <row r="330">
-      <c r="K330" s="12" t="n"/>
+      <c r="L330" s="12" t="n"/>
     </row>
     <row r="331">
-      <c r="K331" s="12" t="n"/>
+      <c r="L331" s="12" t="n"/>
     </row>
     <row r="332">
-      <c r="K332" s="12" t="n"/>
+      <c r="L332" s="12" t="n"/>
     </row>
     <row r="333">
-      <c r="K333" s="12" t="n"/>
+      <c r="L333" s="12" t="n"/>
     </row>
     <row r="334">
-      <c r="K334" s="12" t="n"/>
+      <c r="L334" s="12" t="n"/>
     </row>
     <row r="335">
-      <c r="K335" s="12" t="n"/>
+      <c r="L335" s="12" t="n"/>
     </row>
     <row r="336">
-      <c r="K336" s="12" t="n"/>
+      <c r="L336" s="12" t="n"/>
     </row>
     <row r="337">
-      <c r="K337" s="12" t="n"/>
+      <c r="L337" s="12" t="n"/>
     </row>
     <row r="338">
-      <c r="K338" s="12" t="n"/>
+      <c r="L338" s="12" t="n"/>
     </row>
     <row r="339">
-      <c r="K339" s="12" t="n"/>
+      <c r="L339" s="12" t="n"/>
     </row>
     <row r="340">
-      <c r="K340" s="12" t="n"/>
+      <c r="L340" s="12" t="n"/>
     </row>
     <row r="341">
-      <c r="K341" s="12" t="n"/>
+      <c r="L341" s="12" t="n"/>
     </row>
     <row r="342">
-      <c r="K342" s="12" t="n"/>
+      <c r="L342" s="12" t="n"/>
     </row>
     <row r="343">
-      <c r="K343" s="12" t="n"/>
+      <c r="L343" s="12" t="n"/>
     </row>
     <row r="344">
-      <c r="K344" s="12" t="n"/>
+      <c r="L344" s="12" t="n"/>
     </row>
     <row r="345">
-      <c r="K345" s="12" t="n"/>
+      <c r="L345" s="12" t="n"/>
     </row>
     <row r="346">
-      <c r="K346" s="12" t="n"/>
+      <c r="L346" s="12" t="n"/>
     </row>
     <row r="347">
-      <c r="K347" s="12" t="n"/>
+      <c r="L347" s="12" t="n"/>
     </row>
     <row r="348">
-      <c r="K348" s="12" t="n"/>
+      <c r="L348" s="12" t="n"/>
     </row>
     <row r="349">
-      <c r="K349" s="12" t="n"/>
+      <c r="L349" s="12" t="n"/>
     </row>
     <row r="350">
-      <c r="K350" s="12" t="n"/>
+      <c r="L350" s="12" t="n"/>
     </row>
     <row r="351">
-      <c r="K351" s="12" t="n"/>
+      <c r="L351" s="12" t="n"/>
     </row>
     <row r="352">
-      <c r="K352" s="12" t="n"/>
+      <c r="L352" s="12" t="n"/>
     </row>
     <row r="353">
-      <c r="K353" s="12" t="n"/>
+      <c r="L353" s="12" t="n"/>
     </row>
     <row r="354">
-      <c r="K354" s="12" t="n"/>
+      <c r="L354" s="12" t="n"/>
     </row>
     <row r="355">
-      <c r="K355" s="12" t="n"/>
+      <c r="L355" s="12" t="n"/>
     </row>
     <row r="356">
-      <c r="K356" s="12" t="n"/>
+      <c r="L356" s="12" t="n"/>
     </row>
     <row r="357">
-      <c r="K357" s="12" t="n"/>
+      <c r="L357" s="12" t="n"/>
     </row>
     <row r="358">
-      <c r="K358" s="12" t="n"/>
+      <c r="L358" s="12" t="n"/>
     </row>
     <row r="359">
-      <c r="K359" s="12" t="n"/>
+      <c r="L359" s="12" t="n"/>
     </row>
     <row r="360">
-      <c r="K360" s="12" t="n"/>
+      <c r="L360" s="12" t="n"/>
     </row>
     <row r="361">
-      <c r="K361" s="12" t="n"/>
+      <c r="L361" s="12" t="n"/>
     </row>
     <row r="362">
-      <c r="K362" s="12" t="n"/>
+      <c r="L362" s="12" t="n"/>
     </row>
     <row r="363">
-      <c r="K363" s="12" t="n"/>
+      <c r="L363" s="12" t="n"/>
     </row>
     <row r="364">
-      <c r="K364" s="12" t="n"/>
+      <c r="L364" s="12" t="n"/>
     </row>
     <row r="365">
-      <c r="K365" s="12" t="n"/>
+      <c r="L365" s="12" t="n"/>
     </row>
     <row r="366">
-      <c r="K366" s="12" t="n"/>
+      <c r="L366" s="12" t="n"/>
     </row>
     <row r="367">
-      <c r="K367" s="12" t="n"/>
+      <c r="L367" s="12" t="n"/>
     </row>
     <row r="368">
-      <c r="K368" s="12" t="n"/>
+      <c r="L368" s="12" t="n"/>
     </row>
     <row r="369">
-      <c r="K369" s="12" t="n"/>
+      <c r="L369" s="12" t="n"/>
     </row>
     <row r="370">
-      <c r="K370" s="12" t="n"/>
+      <c r="L370" s="12" t="n"/>
     </row>
     <row r="371">
-      <c r="K371" s="12" t="n"/>
+      <c r="L371" s="12" t="n"/>
     </row>
     <row r="372">
-      <c r="K372" s="12" t="n"/>
+      <c r="L372" s="12" t="n"/>
     </row>
     <row r="373">
-      <c r="K373" s="12" t="n"/>
+      <c r="L373" s="12" t="n"/>
     </row>
     <row r="374">
-      <c r="K374" s="12" t="n"/>
+      <c r="L374" s="12" t="n"/>
     </row>
     <row r="375">
-      <c r="K375" s="12" t="n"/>
+      <c r="L375" s="12" t="n"/>
     </row>
     <row r="376">
-      <c r="K376" s="12" t="n"/>
+      <c r="L376" s="12" t="n"/>
     </row>
     <row r="377">
-      <c r="K377" s="12" t="n"/>
+      <c r="L377" s="12" t="n"/>
     </row>
     <row r="378">
-      <c r="K378" s="12" t="n"/>
+      <c r="L378" s="12" t="n"/>
     </row>
     <row r="379">
-      <c r="K379" s="12" t="n"/>
+      <c r="L379" s="12" t="n"/>
     </row>
     <row r="380">
-      <c r="K380" s="12" t="n"/>
+      <c r="L380" s="12" t="n"/>
     </row>
     <row r="381">
-      <c r="K381" s="12" t="n"/>
+      <c r="L381" s="12" t="n"/>
     </row>
     <row r="382">
-      <c r="K382" s="12" t="n"/>
+      <c r="L382" s="12" t="n"/>
     </row>
     <row r="383">
-      <c r="K383" s="12" t="n"/>
+      <c r="L383" s="12" t="n"/>
     </row>
     <row r="384">
-      <c r="K384" s="12" t="n"/>
+      <c r="L384" s="12" t="n"/>
     </row>
     <row r="385">
-      <c r="K385" s="12" t="n"/>
+      <c r="L385" s="12" t="n"/>
     </row>
     <row r="386">
-      <c r="K386" s="12" t="n"/>
+      <c r="L386" s="12" t="n"/>
     </row>
     <row r="387">
-      <c r="K387" s="12" t="n"/>
+      <c r="L387" s="12" t="n"/>
     </row>
     <row r="388">
-      <c r="K388" s="12" t="n"/>
+      <c r="L388" s="12" t="n"/>
     </row>
     <row r="389">
-      <c r="K389" s="12" t="n"/>
+      <c r="L389" s="12" t="n"/>
     </row>
     <row r="390">
-      <c r="K390" s="12" t="n"/>
+      <c r="L390" s="12" t="n"/>
     </row>
     <row r="391">
-      <c r="K391" s="12" t="n"/>
+      <c r="L391" s="12" t="n"/>
     </row>
     <row r="392">
-      <c r="K392" s="12" t="n"/>
+      <c r="L392" s="12" t="n"/>
     </row>
     <row r="393">
-      <c r="K393" s="12" t="n"/>
+      <c r="L393" s="12" t="n"/>
     </row>
     <row r="394">
-      <c r="K394" s="12" t="n"/>
+      <c r="L394" s="12" t="n"/>
     </row>
     <row r="395">
-      <c r="K395" s="12" t="n"/>
+      <c r="L395" s="12" t="n"/>
     </row>
     <row r="396">
-      <c r="K396" s="12" t="n"/>
+      <c r="L396" s="12" t="n"/>
     </row>
     <row r="397">
-      <c r="K397" s="12" t="n"/>
+      <c r="L397" s="12" t="n"/>
     </row>
     <row r="398">
-      <c r="K398" s="12" t="n"/>
+      <c r="L398" s="12" t="n"/>
     </row>
     <row r="399">
-      <c r="K399" s="12" t="n"/>
+      <c r="L399" s="12" t="n"/>
     </row>
     <row r="400">
-      <c r="K400" s="12" t="n"/>
+      <c r="L400" s="12" t="n"/>
     </row>
     <row r="401">
-      <c r="K401" s="12" t="n"/>
+      <c r="L401" s="12" t="n"/>
     </row>
     <row r="402">
-      <c r="K402" s="12" t="n"/>
+      <c r="L402" s="12" t="n"/>
     </row>
     <row r="403">
-      <c r="K403" s="12" t="n"/>
+      <c r="L403" s="12" t="n"/>
     </row>
     <row r="404">
-      <c r="K404" s="12" t="n"/>
+      <c r="L404" s="12" t="n"/>
     </row>
     <row r="405">
-      <c r="K405" s="12" t="n"/>
+      <c r="L405" s="12" t="n"/>
     </row>
     <row r="406">
-      <c r="K406" s="12" t="n"/>
+      <c r="L406" s="12" t="n"/>
     </row>
     <row r="407">
-      <c r="K407" s="12" t="n"/>
+      <c r="L407" s="12" t="n"/>
     </row>
     <row r="408">
-      <c r="K408" s="12" t="n"/>
+      <c r="L408" s="12" t="n"/>
     </row>
     <row r="409">
-      <c r="K409" s="12" t="n"/>
+      <c r="L409" s="12" t="n"/>
     </row>
     <row r="410">
-      <c r="K410" s="12" t="n"/>
+      <c r="L410" s="12" t="n"/>
     </row>
     <row r="411">
-      <c r="K411" s="12" t="n"/>
+      <c r="L411" s="12" t="n"/>
     </row>
     <row r="412">
-      <c r="K412" s="12" t="n"/>
+      <c r="L412" s="12" t="n"/>
     </row>
     <row r="413">
-      <c r="K413" s="12" t="n"/>
+      <c r="L413" s="12" t="n"/>
     </row>
     <row r="414">
-      <c r="K414" s="12" t="n"/>
+      <c r="L414" s="12" t="n"/>
     </row>
     <row r="415">
-      <c r="K415" s="12" t="n"/>
+      <c r="L415" s="12" t="n"/>
     </row>
     <row r="416">
-      <c r="K416" s="12" t="n"/>
+      <c r="L416" s="12" t="n"/>
     </row>
     <row r="417">
-      <c r="K417" s="12" t="n"/>
+      <c r="L417" s="12" t="n"/>
     </row>
     <row r="418">
-      <c r="K418" s="12" t="n"/>
+      <c r="L418" s="12" t="n"/>
     </row>
     <row r="419">
-      <c r="K419" s="12" t="n"/>
+      <c r="L419" s="12" t="n"/>
     </row>
     <row r="420">
-      <c r="K420" s="12" t="n"/>
+      <c r="L420" s="12" t="n"/>
     </row>
     <row r="421">
-      <c r="K421" s="12" t="n"/>
+      <c r="L421" s="12" t="n"/>
     </row>
     <row r="422">
-      <c r="K422" s="12" t="n"/>
+      <c r="L422" s="12" t="n"/>
     </row>
     <row r="423">
-      <c r="K423" s="12" t="n"/>
+      <c r="L423" s="12" t="n"/>
     </row>
     <row r="424">
-      <c r="K424" s="12" t="n"/>
+      <c r="L424" s="12" t="n"/>
     </row>
     <row r="425">
-      <c r="K425" s="12" t="n"/>
+      <c r="L425" s="12" t="n"/>
     </row>
     <row r="426">
-      <c r="K426" s="12" t="n"/>
+      <c r="L426" s="12" t="n"/>
     </row>
     <row r="427">
-      <c r="K427" s="12" t="n"/>
+      <c r="L427" s="12" t="n"/>
     </row>
     <row r="428">
-      <c r="K428" s="12" t="n"/>
+      <c r="L428" s="12" t="n"/>
     </row>
     <row r="429">
-      <c r="K429" s="12" t="n"/>
+      <c r="L429" s="12" t="n"/>
     </row>
     <row r="430">
-      <c r="K430" s="12" t="n"/>
+      <c r="L430" s="12" t="n"/>
     </row>
     <row r="431">
-      <c r="K431" s="12" t="n"/>
+      <c r="L431" s="12" t="n"/>
     </row>
     <row r="432">
-      <c r="K432" s="12" t="n"/>
+      <c r="L432" s="12" t="n"/>
     </row>
     <row r="433">
-      <c r="K433" s="12" t="n"/>
+      <c r="L433" s="12" t="n"/>
     </row>
     <row r="434">
-      <c r="K434" s="12" t="n"/>
+      <c r="L434" s="12" t="n"/>
     </row>
     <row r="435">
-      <c r="K435" s="12" t="n"/>
+      <c r="L435" s="12" t="n"/>
     </row>
     <row r="436">
-      <c r="K436" s="12" t="n"/>
+      <c r="L436" s="12" t="n"/>
     </row>
     <row r="437">
-      <c r="K437" s="12" t="n"/>
+      <c r="L437" s="12" t="n"/>
     </row>
     <row r="438">
-      <c r="K438" s="12" t="n"/>
+      <c r="L438" s="12" t="n"/>
     </row>
     <row r="439">
-      <c r="K439" s="12" t="n"/>
+      <c r="L439" s="12" t="n"/>
     </row>
     <row r="440">
-      <c r="K440" s="12" t="n"/>
+      <c r="L440" s="12" t="n"/>
     </row>
     <row r="441">
-      <c r="K441" s="12" t="n"/>
+      <c r="L441" s="12" t="n"/>
     </row>
     <row r="442">
-      <c r="K442" s="12" t="n"/>
+      <c r="L442" s="12" t="n"/>
     </row>
     <row r="443">
-      <c r="K443" s="12" t="n"/>
+      <c r="L443" s="12" t="n"/>
     </row>
     <row r="444">
-      <c r="K444" s="12" t="n"/>
+      <c r="L444" s="12" t="n"/>
     </row>
     <row r="445">
-      <c r="K445" s="12" t="n"/>
+      <c r="L445" s="12" t="n"/>
     </row>
     <row r="446">
-      <c r="K446" s="12" t="n"/>
+      <c r="L446" s="12" t="n"/>
     </row>
     <row r="447">
-      <c r="K447" s="12" t="n"/>
+      <c r="L447" s="12" t="n"/>
     </row>
     <row r="448">
-      <c r="K448" s="12" t="n"/>
+      <c r="L448" s="12" t="n"/>
     </row>
     <row r="449">
-      <c r="K449" s="12" t="n"/>
+      <c r="L449" s="12" t="n"/>
     </row>
     <row r="450">
-      <c r="K450" s="12" t="n"/>
+      <c r="L450" s="12" t="n"/>
     </row>
     <row r="451">
-      <c r="K451" s="12" t="n"/>
+      <c r="L451" s="12" t="n"/>
     </row>
     <row r="452">
-      <c r="K452" s="12" t="n"/>
+      <c r="L452" s="12" t="n"/>
     </row>
     <row r="453">
-      <c r="K453" s="12" t="n"/>
+      <c r="L453" s="12" t="n"/>
     </row>
     <row r="454">
-      <c r="K454" s="12" t="n"/>
+      <c r="L454" s="12" t="n"/>
     </row>
     <row r="455">
-      <c r="K455" s="12" t="n"/>
+      <c r="L455" s="12" t="n"/>
     </row>
     <row r="456">
-      <c r="K456" s="12" t="n"/>
+      <c r="L456" s="12" t="n"/>
     </row>
     <row r="457">
-      <c r="K457" s="12" t="n"/>
+      <c r="L457" s="12" t="n"/>
     </row>
     <row r="458">
-      <c r="K458" s="12" t="n"/>
+      <c r="L458" s="12" t="n"/>
     </row>
     <row r="459">
-      <c r="K459" s="12" t="n"/>
+      <c r="L459" s="12" t="n"/>
     </row>
     <row r="460">
-      <c r="K460" s="12" t="n"/>
+      <c r="L460" s="12" t="n"/>
     </row>
     <row r="461">
-      <c r="K461" s="12" t="n"/>
+      <c r="L461" s="12" t="n"/>
     </row>
     <row r="462">
-      <c r="K462" s="12" t="n"/>
+      <c r="L462" s="12" t="n"/>
     </row>
     <row r="463">
-      <c r="K463" s="12" t="n"/>
+      <c r="L463" s="12" t="n"/>
     </row>
     <row r="464">
-      <c r="K464" s="12" t="n"/>
+      <c r="L464" s="12" t="n"/>
     </row>
     <row r="465">
-      <c r="K465" s="12" t="n"/>
+      <c r="L465" s="12" t="n"/>
     </row>
     <row r="466">
-      <c r="K466" s="12" t="n"/>
+      <c r="L466" s="12" t="n"/>
     </row>
     <row r="467">
-      <c r="K467" s="12" t="n"/>
+      <c r="L467" s="12" t="n"/>
     </row>
     <row r="468">
-      <c r="K468" s="12" t="n"/>
+      <c r="L468" s="12" t="n"/>
     </row>
     <row r="469">
-      <c r="K469" s="12" t="n"/>
+      <c r="L469" s="12" t="n"/>
     </row>
     <row r="470">
-      <c r="K470" s="12" t="n"/>
+      <c r="L470" s="12" t="n"/>
     </row>
     <row r="471">
-      <c r="K471" s="12" t="n"/>
+      <c r="L471" s="12" t="n"/>
     </row>
     <row r="472">
-      <c r="K472" s="12" t="n"/>
+      <c r="L472" s="12" t="n"/>
     </row>
     <row r="473">
-      <c r="K473" s="12" t="n"/>
+      <c r="L473" s="12" t="n"/>
     </row>
     <row r="474">
-      <c r="K474" s="12" t="n"/>
+      <c r="L474" s="12" t="n"/>
     </row>
     <row r="475">
-      <c r="K475" s="12" t="n"/>
+      <c r="L475" s="12" t="n"/>
     </row>
     <row r="476">
-      <c r="K476" s="12" t="n"/>
+      <c r="L476" s="12" t="n"/>
     </row>
     <row r="477">
-      <c r="K477" s="12" t="n"/>
+      <c r="L477" s="12" t="n"/>
     </row>
     <row r="478">
-      <c r="K478" s="12" t="n"/>
+      <c r="L478" s="12" t="n"/>
     </row>
     <row r="479">
-      <c r="K479" s="12" t="n"/>
+      <c r="L479" s="12" t="n"/>
     </row>
     <row r="480">
-      <c r="K480" s="12" t="n"/>
+      <c r="L480" s="12" t="n"/>
     </row>
     <row r="481">
-      <c r="K481" s="12" t="n"/>
+      <c r="L481" s="12" t="n"/>
     </row>
     <row r="482">
-      <c r="K482" s="12" t="n"/>
+      <c r="L482" s="12" t="n"/>
     </row>
     <row r="483">
-      <c r="K483" s="12" t="n"/>
+      <c r="L483" s="12" t="n"/>
     </row>
     <row r="484">
-      <c r="K484" s="12" t="n"/>
+      <c r="L484" s="12" t="n"/>
     </row>
     <row r="485">
-      <c r="K485" s="12" t="n"/>
+      <c r="L485" s="12" t="n"/>
     </row>
     <row r="486">
-      <c r="K486" s="12" t="n"/>
+      <c r="L486" s="12" t="n"/>
     </row>
     <row r="487">
-      <c r="K487" s="12" t="n"/>
+      <c r="L487" s="12" t="n"/>
     </row>
     <row r="488">
-      <c r="K488" s="12" t="n"/>
+      <c r="L488" s="12" t="n"/>
     </row>
     <row r="489">
-      <c r="K489" s="12" t="n"/>
+      <c r="L489" s="12" t="n"/>
     </row>
     <row r="490">
-      <c r="K490" s="12" t="n"/>
+      <c r="L490" s="12" t="n"/>
     </row>
     <row r="491">
-      <c r="K491" s="12" t="n"/>
+      <c r="L491" s="12" t="n"/>
     </row>
     <row r="492">
-      <c r="K492" s="12" t="n"/>
+      <c r="L492" s="12" t="n"/>
     </row>
     <row r="493">
-      <c r="K493" s="12" t="n"/>
+      <c r="L493" s="12" t="n"/>
     </row>
     <row r="494">
-      <c r="K494" s="12" t="n"/>
+      <c r="L494" s="12" t="n"/>
     </row>
     <row r="495">
-      <c r="K495" s="12" t="n"/>
+      <c r="L495" s="12" t="n"/>
     </row>
     <row r="496">
-      <c r="K496" s="12" t="n"/>
+      <c r="L496" s="12" t="n"/>
     </row>
     <row r="497">
-      <c r="K497" s="12" t="n"/>
+      <c r="L497" s="12" t="n"/>
     </row>
     <row r="498">
-      <c r="K498" s="12" t="n"/>
+      <c r="L498" s="12" t="n"/>
     </row>
     <row r="499">
-      <c r="K499" s="12" t="n"/>
+      <c r="L499" s="12" t="n"/>
     </row>
     <row r="500">
-      <c r="K500" s="12" t="n"/>
+      <c r="L500" s="12" t="n"/>
     </row>
     <row r="501">
-      <c r="K501" s="12" t="n"/>
+      <c r="L501" s="12" t="n"/>
     </row>
     <row r="502">
-      <c r="K502" s="12" t="n"/>
+      <c r="L502" s="12" t="n"/>
     </row>
     <row r="503">
-      <c r="K503" s="12" t="n"/>
+      <c r="L503" s="12" t="n"/>
     </row>
     <row r="504">
-      <c r="K504" s="12" t="n"/>
+      <c r="L504" s="12" t="n"/>
     </row>
     <row r="505">
-      <c r="K505" s="12" t="n"/>
+      <c r="L505" s="12" t="n"/>
     </row>
     <row r="506">
-      <c r="K506" s="12" t="n"/>
+      <c r="L506" s="12" t="n"/>
     </row>
     <row r="507">
-      <c r="K507" s="12" t="n"/>
+      <c r="L507" s="12" t="n"/>
     </row>
     <row r="508">
-      <c r="K508" s="12" t="n"/>
+      <c r="L508" s="12" t="n"/>
     </row>
     <row r="509">
-      <c r="K509" s="12" t="n"/>
+      <c r="L509" s="12" t="n"/>
     </row>
     <row r="510">
-      <c r="K510" s="12" t="n"/>
+      <c r="L510" s="12" t="n"/>
     </row>
     <row r="511">
-      <c r="K511" s="12" t="n"/>
+      <c r="L511" s="12" t="n"/>
     </row>
     <row r="512">
-      <c r="K512" s="12" t="n"/>
+      <c r="L512" s="12" t="n"/>
     </row>
     <row r="513">
-      <c r="K513" s="12" t="n"/>
+      <c r="L513" s="12" t="n"/>
     </row>
     <row r="514">
-      <c r="K514" s="12" t="n"/>
+      <c r="L514" s="12" t="n"/>
     </row>
     <row r="515">
-      <c r="K515" s="12" t="n"/>
+      <c r="L515" s="12" t="n"/>
     </row>
     <row r="516">
-      <c r="K516" s="12" t="n"/>
+      <c r="L516" s="12" t="n"/>
     </row>
     <row r="517">
-      <c r="K517" s="12" t="n"/>
+      <c r="L517" s="12" t="n"/>
     </row>
     <row r="518">
-      <c r="K518" s="12" t="n"/>
+      <c r="L518" s="12" t="n"/>
     </row>
     <row r="519">
-      <c r="K519" s="12" t="n"/>
+      <c r="L519" s="12" t="n"/>
     </row>
     <row r="520">
-      <c r="K520" s="12" t="n"/>
+      <c r="L520" s="12" t="n"/>
     </row>
     <row r="521">
-      <c r="K521" s="12" t="n"/>
+      <c r="L521" s="12" t="n"/>
     </row>
     <row r="522">
-      <c r="K522" s="12" t="n"/>
+      <c r="L522" s="12" t="n"/>
     </row>
     <row r="523">
-      <c r="K523" s="12" t="n"/>
+      <c r="L523" s="12" t="n"/>
     </row>
     <row r="524">
-      <c r="K524" s="12" t="n"/>
+      <c r="L524" s="12" t="n"/>
     </row>
     <row r="525">
-      <c r="K525" s="12" t="n"/>
+      <c r="L525" s="12" t="n"/>
     </row>
     <row r="526">
-      <c r="K526" s="12" t="n"/>
+      <c r="L526" s="12" t="n"/>
     </row>
     <row r="527">
-      <c r="K527" s="12" t="n"/>
+      <c r="L527" s="12" t="n"/>
     </row>
     <row r="528">
-      <c r="K528" s="12" t="n"/>
+      <c r="L528" s="12" t="n"/>
     </row>
     <row r="529">
-      <c r="K529" s="12" t="n"/>
+      <c r="L529" s="12" t="n"/>
     </row>
     <row r="530">
-      <c r="K530" s="12" t="n"/>
+      <c r="L530" s="12" t="n"/>
     </row>
     <row r="531">
-      <c r="K531" s="12" t="n"/>
+      <c r="L531" s="12" t="n"/>
     </row>
     <row r="532">
-      <c r="K532" s="12" t="n"/>
+      <c r="L532" s="12" t="n"/>
     </row>
     <row r="533">
-      <c r="K533" s="12" t="n"/>
+      <c r="L533" s="12" t="n"/>
     </row>
     <row r="534">
-      <c r="K534" s="12" t="n"/>
+      <c r="L534" s="12" t="n"/>
     </row>
     <row r="535">
-      <c r="K535" s="12" t="n"/>
+      <c r="L535" s="12" t="n"/>
     </row>
     <row r="536">
-      <c r="K536" s="12" t="n"/>
+      <c r="L536" s="12" t="n"/>
     </row>
     <row r="537">
-      <c r="K537" s="12" t="n"/>
+      <c r="L537" s="12" t="n"/>
     </row>
     <row r="538">
-      <c r="K538" s="12" t="n"/>
+      <c r="L538" s="12" t="n"/>
     </row>
     <row r="539">
-      <c r="K539" s="12" t="n"/>
+      <c r="L539" s="12" t="n"/>
     </row>
     <row r="540">
-      <c r="K540" s="12" t="n"/>
+      <c r="L540" s="12" t="n"/>
     </row>
     <row r="541">
-      <c r="K541" s="12" t="n"/>
+      <c r="L541" s="12" t="n"/>
     </row>
     <row r="542">
-      <c r="K542" s="12" t="n"/>
+      <c r="L542" s="12" t="n"/>
     </row>
     <row r="543">
-      <c r="K543" s="12" t="n"/>
+      <c r="L543" s="12" t="n"/>
     </row>
     <row r="544">
-      <c r="K544" s="12" t="n"/>
+      <c r="L544" s="12" t="n"/>
     </row>
     <row r="545">
-      <c r="K545" s="12" t="n"/>
+      <c r="L545" s="12" t="n"/>
     </row>
     <row r="546">
-      <c r="K546" s="12" t="n"/>
+      <c r="L546" s="12" t="n"/>
     </row>
     <row r="547">
-      <c r="K547" s="12" t="n"/>
+      <c r="L547" s="12" t="n"/>
     </row>
     <row r="548">
-      <c r="K548" s="12" t="n"/>
+      <c r="L548" s="12" t="n"/>
     </row>
     <row r="549">
-      <c r="K549" s="12" t="n"/>
+      <c r="L549" s="12" t="n"/>
     </row>
     <row r="550">
-      <c r="K550" s="12" t="n"/>
+      <c r="L550" s="12" t="n"/>
     </row>
     <row r="551">
-      <c r="K551" s="12" t="n"/>
+      <c r="L551" s="12" t="n"/>
     </row>
     <row r="552">
-      <c r="K552" s="12" t="n"/>
+      <c r="L552" s="12" t="n"/>
     </row>
     <row r="553">
-      <c r="K553" s="12" t="n"/>
+      <c r="L553" s="12" t="n"/>
     </row>
     <row r="554">
-      <c r="K554" s="12" t="n"/>
+      <c r="L554" s="12" t="n"/>
     </row>
     <row r="555">
-      <c r="K555" s="12" t="n"/>
+      <c r="L555" s="12" t="n"/>
     </row>
     <row r="556">
-      <c r="K556" s="12" t="n"/>
+      <c r="L556" s="12" t="n"/>
     </row>
     <row r="557">
-      <c r="K557" s="12" t="n"/>
+      <c r="L557" s="12" t="n"/>
     </row>
     <row r="558">
-      <c r="K558" s="12" t="n"/>
+      <c r="L558" s="12" t="n"/>
     </row>
     <row r="559">
-      <c r="K559" s="12" t="n"/>
+      <c r="L559" s="12" t="n"/>
     </row>
     <row r="560">
-      <c r="K560" s="12" t="n"/>
+      <c r="L560" s="12" t="n"/>
     </row>
     <row r="561">
-      <c r="K561" s="12" t="n"/>
+      <c r="L561" s="12" t="n"/>
     </row>
     <row r="562">
-      <c r="K562" s="12" t="n"/>
+      <c r="L562" s="12" t="n"/>
     </row>
     <row r="563">
-      <c r="K563" s="12" t="n"/>
+      <c r="L563" s="12" t="n"/>
     </row>
     <row r="564">
-      <c r="K564" s="12" t="n"/>
+      <c r="L564" s="12" t="n"/>
     </row>
     <row r="565">
-      <c r="K565" s="12" t="n"/>
+      <c r="L565" s="12" t="n"/>
     </row>
     <row r="566">
-      <c r="K566" s="12" t="n"/>
+      <c r="L566" s="12" t="n"/>
     </row>
     <row r="567">
-      <c r="K567" s="12" t="n"/>
+      <c r="L567" s="12" t="n"/>
     </row>
     <row r="568">
-      <c r="K568" s="12" t="n"/>
+      <c r="L568" s="12" t="n"/>
     </row>
     <row r="569">
-      <c r="K569" s="12" t="n"/>
+      <c r="L569" s="12" t="n"/>
     </row>
     <row r="570">
-      <c r="K570" s="12" t="n"/>
+      <c r="L570" s="12" t="n"/>
     </row>
     <row r="571">
-      <c r="K571" s="12" t="n"/>
+      <c r="L571" s="12" t="n"/>
     </row>
     <row r="572">
-      <c r="K572" s="12" t="n"/>
+      <c r="L572" s="12" t="n"/>
     </row>
     <row r="573">
-      <c r="K573" s="12" t="n"/>
+      <c r="L573" s="12" t="n"/>
     </row>
     <row r="574">
-      <c r="K574" s="12" t="n"/>
+      <c r="L574" s="12" t="n"/>
     </row>
     <row r="575">
-      <c r="K575" s="12" t="n"/>
+      <c r="L575" s="12" t="n"/>
     </row>
     <row r="576">
-      <c r="K576" s="12" t="n"/>
+      <c r="L576" s="12" t="n"/>
     </row>
     <row r="577">
-      <c r="K577" s="12" t="n"/>
+      <c r="L577" s="12" t="n"/>
     </row>
     <row r="578">
-      <c r="K578" s="12" t="n"/>
+      <c r="L578" s="12" t="n"/>
     </row>
     <row r="579">
-      <c r="K579" s="12" t="n"/>
+      <c r="L579" s="12" t="n"/>
     </row>
     <row r="580">
-      <c r="K580" s="12" t="n"/>
+      <c r="L580" s="12" t="n"/>
     </row>
     <row r="581">
-      <c r="K581" s="12" t="n"/>
+      <c r="L581" s="12" t="n"/>
     </row>
     <row r="582">
-      <c r="K582" s="12" t="n"/>
+      <c r="L582" s="12" t="n"/>
     </row>
     <row r="583">
-      <c r="K583" s="12" t="n"/>
+      <c r="L583" s="12" t="n"/>
     </row>
     <row r="584">
-      <c r="K584" s="12" t="n"/>
+      <c r="L584" s="12" t="n"/>
     </row>
     <row r="585">
-      <c r="K585" s="12" t="n"/>
+      <c r="L585" s="12" t="n"/>
     </row>
     <row r="586">
-      <c r="K586" s="12" t="n"/>
+      <c r="L586" s="12" t="n"/>
     </row>
     <row r="587">
-      <c r="K587" s="12" t="n"/>
+      <c r="L587" s="12" t="n"/>
     </row>
     <row r="588">
-      <c r="K588" s="12" t="n"/>
+      <c r="L588" s="12" t="n"/>
     </row>
     <row r="589">
-      <c r="K589" s="12" t="n"/>
+      <c r="L589" s="12" t="n"/>
     </row>
     <row r="590">
-      <c r="K590" s="12" t="n"/>
+      <c r="L590" s="12" t="n"/>
     </row>
     <row r="591">
-      <c r="K591" s="12" t="n"/>
+      <c r="L591" s="12" t="n"/>
     </row>
     <row r="592">
-      <c r="K592" s="12" t="n"/>
+      <c r="L592" s="12" t="n"/>
     </row>
     <row r="593">
-      <c r="K593" s="12" t="n"/>
+      <c r="L593" s="12" t="n"/>
     </row>
     <row r="594">
-      <c r="K594" s="12" t="n"/>
+      <c r="L594" s="12" t="n"/>
     </row>
     <row r="595">
-      <c r="K595" s="12" t="n"/>
+      <c r="L595" s="12" t="n"/>
     </row>
     <row r="596">
-      <c r="K596" s="12" t="n"/>
+      <c r="L596" s="12" t="n"/>
     </row>
     <row r="597">
-      <c r="K597" s="12" t="n"/>
+      <c r="L597" s="12" t="n"/>
     </row>
     <row r="598">
-      <c r="K598" s="12" t="n"/>
+      <c r="L598" s="12" t="n"/>
     </row>
     <row r="599">
-      <c r="K599" s="12" t="n"/>
+      <c r="L599" s="12" t="n"/>
     </row>
     <row r="600">
-      <c r="K600" s="12" t="n"/>
+      <c r="L600" s="12" t="n"/>
     </row>
     <row r="601">
-      <c r="K601" s="12" t="n"/>
+      <c r="L601" s="12" t="n"/>
     </row>
     <row r="602">
-      <c r="K602" s="12" t="n"/>
+      <c r="L602" s="12" t="n"/>
     </row>
     <row r="603">
-      <c r="K603" s="12" t="n"/>
+      <c r="L603" s="12" t="n"/>
     </row>
     <row r="604">
-      <c r="K604" s="12" t="n"/>
+      <c r="L604" s="12" t="n"/>
     </row>
     <row r="605">
-      <c r="K605" s="12" t="n"/>
+      <c r="L605" s="12" t="n"/>
     </row>
     <row r="606">
-      <c r="K606" s="12" t="n"/>
+      <c r="L606" s="12" t="n"/>
     </row>
     <row r="607">
-      <c r="K607" s="12" t="n"/>
+      <c r="L607" s="12" t="n"/>
     </row>
     <row r="608">
-      <c r="K608" s="12" t="n"/>
+      <c r="L608" s="12" t="n"/>
     </row>
     <row r="609">
-      <c r="K609" s="12" t="n"/>
+      <c r="L609" s="12" t="n"/>
     </row>
     <row r="610">
-      <c r="K610" s="12" t="n"/>
+      <c r="L610" s="12" t="n"/>
     </row>
     <row r="611">
-      <c r="K611" s="12" t="n"/>
+      <c r="L611" s="12" t="n"/>
     </row>
     <row r="612">
-      <c r="K612" s="12" t="n"/>
+      <c r="L612" s="12" t="n"/>
     </row>
     <row r="613">
-      <c r="K613" s="12" t="n"/>
+      <c r="L613" s="12" t="n"/>
     </row>
     <row r="614">
-      <c r="K614" s="12" t="n"/>
+      <c r="L614" s="12" t="n"/>
     </row>
     <row r="615">
-      <c r="K615" s="12" t="n"/>
+      <c r="L615" s="12" t="n"/>
     </row>
     <row r="616">
-      <c r="K616" s="12" t="n"/>
+      <c r="L616" s="12" t="n"/>
     </row>
     <row r="617">
-      <c r="K617" s="12" t="n"/>
+      <c r="L617" s="12" t="n"/>
     </row>
     <row r="618">
-      <c r="K618" s="12" t="n"/>
+      <c r="L618" s="12" t="n"/>
     </row>
     <row r="619">
-      <c r="K619" s="12" t="n"/>
+      <c r="L619" s="12" t="n"/>
     </row>
     <row r="620">
-      <c r="K620" s="12" t="n"/>
+      <c r="L620" s="12" t="n"/>
     </row>
     <row r="621">
-      <c r="K621" s="12" t="n"/>
+      <c r="L621" s="12" t="n"/>
     </row>
     <row r="622">
-      <c r="K622" s="12" t="n"/>
+      <c r="L622" s="12" t="n"/>
     </row>
     <row r="623">
-      <c r="K623" s="12" t="n"/>
+      <c r="L623" s="12" t="n"/>
     </row>
     <row r="624">
-      <c r="K624" s="12" t="n"/>
+      <c r="L624" s="12" t="n"/>
     </row>
     <row r="625">
-      <c r="K625" s="12" t="n"/>
+      <c r="L625" s="12" t="n"/>
     </row>
     <row r="626">
-      <c r="K626" s="12" t="n"/>
+      <c r="L626" s="12" t="n"/>
     </row>
     <row r="627">
-      <c r="K627" s="12" t="n"/>
+      <c r="L627" s="12" t="n"/>
     </row>
     <row r="628">
-      <c r="K628" s="12" t="n"/>
+      <c r="L628" s="12" t="n"/>
     </row>
     <row r="629">
-      <c r="K629" s="12" t="n"/>
+      <c r="L629" s="12" t="n"/>
     </row>
     <row r="630">
-      <c r="K630" s="12" t="n"/>
+      <c r="L630" s="12" t="n"/>
     </row>
     <row r="631">
-      <c r="K631" s="12" t="n"/>
+      <c r="L631" s="12" t="n"/>
     </row>
     <row r="632">
-      <c r="K632" s="12" t="n"/>
+      <c r="L632" s="12" t="n"/>
     </row>
     <row r="633">
-      <c r="K633" s="12" t="n"/>
+      <c r="L633" s="12" t="n"/>
     </row>
     <row r="634">
-      <c r="K634" s="12" t="n"/>
+      <c r="L634" s="12" t="n"/>
     </row>
     <row r="635">
-      <c r="K635" s="12" t="n"/>
+      <c r="L635" s="12" t="n"/>
     </row>
     <row r="636">
-      <c r="K636" s="12" t="n"/>
+      <c r="L636" s="12" t="n"/>
     </row>
     <row r="637">
-      <c r="K637" s="12" t="n"/>
+      <c r="L637" s="12" t="n"/>
     </row>
     <row r="638">
-      <c r="K638" s="12" t="n"/>
+      <c r="L638" s="12" t="n"/>
     </row>
     <row r="639">
-      <c r="K639" s="12" t="n"/>
+      <c r="L639" s="12" t="n"/>
     </row>
     <row r="640">
-      <c r="K640" s="12" t="n"/>
+      <c r="L640" s="12" t="n"/>
     </row>
     <row r="641">
-      <c r="K641" s="12" t="n"/>
+      <c r="L641" s="12" t="n"/>
     </row>
     <row r="642">
-      <c r="K642" s="12" t="n"/>
+      <c r="L642" s="12" t="n"/>
     </row>
     <row r="643">
-      <c r="K643" s="12" t="n"/>
+      <c r="L643" s="12" t="n"/>
     </row>
     <row r="644">
-      <c r="K644" s="12" t="n"/>
+      <c r="L644" s="12" t="n"/>
     </row>
     <row r="645">
-      <c r="K645" s="12" t="n"/>
+      <c r="L645" s="12" t="n"/>
     </row>
     <row r="646">
-      <c r="K646" s="12" t="n"/>
+      <c r="L646" s="12" t="n"/>
     </row>
     <row r="647">
-      <c r="K647" s="12" t="n"/>
+      <c r="L647" s="12" t="n"/>
     </row>
     <row r="648">
-      <c r="K648" s="12" t="n"/>
+      <c r="L648" s="12" t="n"/>
     </row>
     <row r="649">
-      <c r="K649" s="12" t="n"/>
+      <c r="L649" s="12" t="n"/>
     </row>
     <row r="650">
-      <c r="K650" s="12" t="n"/>
+      <c r="L650" s="12" t="n"/>
     </row>
     <row r="651">
-      <c r="K651" s="12" t="n"/>
+      <c r="L651" s="12" t="n"/>
     </row>
     <row r="652">
-      <c r="K652" s="12" t="n"/>
+      <c r="L652" s="12" t="n"/>
     </row>
     <row r="653">
-      <c r="K653" s="12" t="n"/>
+      <c r="L653" s="12" t="n"/>
     </row>
     <row r="654">
-      <c r="K654" s="12" t="n"/>
+      <c r="L654" s="12" t="n"/>
     </row>
     <row r="655">
-      <c r="K655" s="12" t="n"/>
+      <c r="L655" s="12" t="n"/>
     </row>
     <row r="656">
-      <c r="K656" s="12" t="n"/>
+      <c r="L656" s="12" t="n"/>
     </row>
     <row r="657">
-      <c r="K657" s="12" t="n"/>
+      <c r="L657" s="12" t="n"/>
     </row>
     <row r="658">
-      <c r="K658" s="12" t="n"/>
+      <c r="L658" s="12" t="n"/>
     </row>
     <row r="659">
-      <c r="K659" s="12" t="n"/>
+      <c r="L659" s="12" t="n"/>
     </row>
     <row r="660">
-      <c r="K660" s="12" t="n"/>
+      <c r="L660" s="12" t="n"/>
     </row>
     <row r="661">
-      <c r="K661" s="12" t="n"/>
+      <c r="L661" s="12" t="n"/>
     </row>
     <row r="662">
-      <c r="K662" s="12" t="n"/>
+      <c r="L662" s="12" t="n"/>
     </row>
     <row r="663">
-      <c r="K663" s="12" t="n"/>
+      <c r="L663" s="12" t="n"/>
     </row>
     <row r="664">
-      <c r="K664" s="12" t="n"/>
+      <c r="L664" s="12" t="n"/>
     </row>
     <row r="665">
-      <c r="K665" s="12" t="n"/>
+      <c r="L665" s="12" t="n"/>
     </row>
     <row r="666">
-      <c r="K666" s="12" t="n"/>
+      <c r="L666" s="12" t="n"/>
     </row>
     <row r="667">
-      <c r="K667" s="12" t="n"/>
+      <c r="L667" s="12" t="n"/>
     </row>
     <row r="668">
-      <c r="K668" s="12" t="n"/>
+      <c r="L668" s="12" t="n"/>
     </row>
     <row r="669">
-      <c r="K669" s="12" t="n"/>
+      <c r="L669" s="12" t="n"/>
     </row>
     <row r="670">
-      <c r="K670" s="12" t="n"/>
+      <c r="L670" s="12" t="n"/>
     </row>
     <row r="671">
-      <c r="K671" s="12" t="n"/>
+      <c r="L671" s="12" t="n"/>
     </row>
     <row r="672">
-      <c r="K672" s="12" t="n"/>
+      <c r="L672" s="12" t="n"/>
     </row>
     <row r="673">
-      <c r="K673" s="12" t="n"/>
+      <c r="L673" s="12" t="n"/>
     </row>
     <row r="674">
-      <c r="K674" s="12" t="n"/>
+      <c r="L674" s="12" t="n"/>
     </row>
     <row r="675">
-      <c r="K675" s="12" t="n"/>
+      <c r="L675" s="12" t="n"/>
     </row>
     <row r="676">
-      <c r="K676" s="12" t="n"/>
+      <c r="L676" s="12" t="n"/>
     </row>
     <row r="677">
-      <c r="K677" s="12" t="n"/>
+      <c r="L677" s="12" t="n"/>
     </row>
     <row r="678">
-      <c r="K678" s="12" t="n"/>
+      <c r="L678" s="12" t="n"/>
     </row>
     <row r="679">
-      <c r="K679" s="12" t="n"/>
+      <c r="L679" s="12" t="n"/>
     </row>
     <row r="680">
-      <c r="K680" s="12" t="n"/>
+      <c r="L680" s="12" t="n"/>
     </row>
     <row r="681">
-      <c r="K681" s="12" t="n"/>
+      <c r="L681" s="12" t="n"/>
     </row>
     <row r="682">
-      <c r="K682" s="12" t="n"/>
+      <c r="L682" s="12" t="n"/>
     </row>
     <row r="683">
-      <c r="K683" s="12" t="n"/>
+      <c r="L683" s="12" t="n"/>
     </row>
     <row r="684">
-      <c r="K684" s="12" t="n"/>
+      <c r="L684" s="12" t="n"/>
     </row>
     <row r="685">
-      <c r="K685" s="12" t="n"/>
+      <c r="L685" s="12" t="n"/>
     </row>
     <row r="686">
-      <c r="K686" s="12" t="n"/>
+      <c r="L686" s="12" t="n"/>
     </row>
     <row r="687">
-      <c r="K687" s="12" t="n"/>
+      <c r="L687" s="12" t="n"/>
     </row>
     <row r="688">
-      <c r="K688" s="12" t="n"/>
+      <c r="L688" s="12" t="n"/>
     </row>
     <row r="689">
-      <c r="K689" s="12" t="n"/>
+      <c r="L689" s="12" t="n"/>
     </row>
     <row r="690">
-      <c r="K690" s="12" t="n"/>
+      <c r="L690" s="12" t="n"/>
     </row>
     <row r="691">
-      <c r="K691" s="12" t="n"/>
+      <c r="L691" s="12" t="n"/>
     </row>
     <row r="692">
-      <c r="K692" s="12" t="n"/>
+      <c r="L692" s="12" t="n"/>
     </row>
     <row r="693">
-      <c r="K693" s="12" t="n"/>
+      <c r="L693" s="12" t="n"/>
     </row>
     <row r="694">
-      <c r="K694" s="12" t="n"/>
+      <c r="L694" s="12" t="n"/>
     </row>
     <row r="695">
-      <c r="K695" s="12" t="n"/>
+      <c r="L695" s="12" t="n"/>
     </row>
     <row r="696">
-      <c r="K696" s="12" t="n"/>
+      <c r="L696" s="12" t="n"/>
     </row>
     <row r="697">
-      <c r="K697" s="12" t="n"/>
+      <c r="L697" s="12" t="n"/>
     </row>
     <row r="698">
-      <c r="K698" s="12" t="n"/>
+      <c r="L698" s="12" t="n"/>
     </row>
     <row r="699">
-      <c r="K699" s="12" t="n"/>
+      <c r="L699" s="12" t="n"/>
     </row>
     <row r="700">
-      <c r="K700" s="12" t="n"/>
+      <c r="L700" s="12" t="n"/>
     </row>
     <row r="701">
-      <c r="K701" s="12" t="n"/>
+      <c r="L701" s="12" t="n"/>
     </row>
     <row r="702">
-      <c r="K702" s="12" t="n"/>
+      <c r="L702" s="12" t="n"/>
     </row>
     <row r="703">
-      <c r="K703" s="12" t="n"/>
+      <c r="L703" s="12" t="n"/>
     </row>
     <row r="704">
-      <c r="K704" s="12" t="n"/>
+      <c r="L704" s="12" t="n"/>
     </row>
     <row r="705">
-      <c r="K705" s="12" t="n"/>
+      <c r="L705" s="12" t="n"/>
     </row>
     <row r="706">
-      <c r="K706" s="12" t="n"/>
+      <c r="L706" s="12" t="n"/>
     </row>
     <row r="707">
-      <c r="K707" s="12" t="n"/>
+      <c r="L707" s="12" t="n"/>
     </row>
     <row r="708">
-      <c r="K708" s="12" t="n"/>
+      <c r="L708" s="12" t="n"/>
     </row>
     <row r="709">
-      <c r="K709" s="12" t="n"/>
+      <c r="L709" s="12" t="n"/>
     </row>
     <row r="710">
-      <c r="K710" s="12" t="n"/>
+      <c r="L710" s="12" t="n"/>
     </row>
     <row r="711">
-      <c r="K711" s="12" t="n"/>
+      <c r="L711" s="12" t="n"/>
     </row>
     <row r="712">
-      <c r="K712" s="12" t="n"/>
+      <c r="L712" s="12" t="n"/>
     </row>
     <row r="713">
-      <c r="K713" s="12" t="n"/>
+      <c r="L713" s="12" t="n"/>
     </row>
     <row r="714">
-      <c r="K714" s="12" t="n"/>
+      <c r="L714" s="12" t="n"/>
     </row>
     <row r="715">
-      <c r="K715" s="12" t="n"/>
+      <c r="L715" s="12" t="n"/>
     </row>
     <row r="716">
-      <c r="K716" s="12" t="n"/>
+      <c r="L716" s="12" t="n"/>
     </row>
     <row r="717">
-      <c r="K717" s="12" t="n"/>
+      <c r="L717" s="12" t="n"/>
     </row>
     <row r="718">
-      <c r="K718" s="12" t="n"/>
+      <c r="L718" s="12" t="n"/>
     </row>
     <row r="719">
-      <c r="K719" s="12" t="n"/>
+      <c r="L719" s="12" t="n"/>
     </row>
     <row r="720">
-      <c r="K720" s="12" t="n"/>
+      <c r="L720" s="12" t="n"/>
     </row>
     <row r="721">
-      <c r="K721" s="12" t="n"/>
+      <c r="L721" s="12" t="n"/>
     </row>
     <row r="722">
-      <c r="K722" s="12" t="n"/>
+      <c r="L722" s="12" t="n"/>
     </row>
     <row r="723">
-      <c r="K723" s="12" t="n"/>
+      <c r="L723" s="12" t="n"/>
     </row>
     <row r="724">
-      <c r="K724" s="12" t="n"/>
+      <c r="L724" s="12" t="n"/>
     </row>
     <row r="725">
-      <c r="K725" s="12" t="n"/>
+      <c r="L725" s="12" t="n"/>
     </row>
     <row r="726">
-      <c r="K726" s="12" t="n"/>
+      <c r="L726" s="12" t="n"/>
     </row>
     <row r="727">
-      <c r="K727" s="12" t="n"/>
+      <c r="L727" s="12" t="n"/>
     </row>
     <row r="728">
-      <c r="K728" s="12" t="n"/>
+      <c r="L728" s="12" t="n"/>
     </row>
     <row r="729">
-      <c r="K729" s="12" t="n"/>
+      <c r="L729" s="12" t="n"/>
     </row>
     <row r="730">
-      <c r="K730" s="12" t="n"/>
+      <c r="L730" s="12" t="n"/>
     </row>
     <row r="731">
-      <c r="K731" s="12" t="n"/>
+      <c r="L731" s="12" t="n"/>
     </row>
     <row r="732">
-      <c r="K732" s="12" t="n"/>
+      <c r="L732" s="12" t="n"/>
     </row>
     <row r="733">
-      <c r="K733" s="12" t="n"/>
+      <c r="L733" s="12" t="n"/>
     </row>
     <row r="734">
-      <c r="K734" s="12" t="n"/>
+      <c r="L734" s="12" t="n"/>
     </row>
     <row r="735">
-      <c r="K735" s="12" t="n"/>
+      <c r="L735" s="12" t="n"/>
     </row>
     <row r="736">
-      <c r="K736" s="12" t="n"/>
+      <c r="L736" s="12" t="n"/>
     </row>
     <row r="737">
-      <c r="K737" s="12" t="n"/>
+      <c r="L737" s="12" t="n"/>
     </row>
     <row r="738">
-      <c r="K738" s="12" t="n"/>
+      <c r="L738" s="12" t="n"/>
     </row>
     <row r="739">
-      <c r="K739" s="12" t="n"/>
+      <c r="L739" s="12" t="n"/>
     </row>
     <row r="740">
-      <c r="K740" s="12" t="n"/>
+      <c r="L740" s="12" t="n"/>
     </row>
     <row r="741">
-      <c r="K741" s="12" t="n"/>
+      <c r="L741" s="12" t="n"/>
     </row>
     <row r="742">
-      <c r="K742" s="12" t="n"/>
+      <c r="L742" s="12" t="n"/>
     </row>
     <row r="743">
-      <c r="K743" s="12" t="n"/>
+      <c r="L743" s="12" t="n"/>
     </row>
     <row r="744">
-      <c r="K744" s="12" t="n"/>
+      <c r="L744" s="12" t="n"/>
     </row>
     <row r="745">
-      <c r="K745" s="12" t="n"/>
+      <c r="L745" s="12" t="n"/>
     </row>
     <row r="746">
-      <c r="K746" s="12" t="n"/>
+      <c r="L746" s="12" t="n"/>
     </row>
     <row r="747">
-      <c r="K747" s="12" t="n"/>
+      <c r="L747" s="12" t="n"/>
     </row>
     <row r="748">
-      <c r="K748" s="12" t="n"/>
+      <c r="L748" s="12" t="n"/>
     </row>
     <row r="749">
-      <c r="K749" s="12" t="n"/>
+      <c r="L749" s="12" t="n"/>
     </row>
     <row r="750">
-      <c r="K750" s="12" t="n"/>
+      <c r="L750" s="12" t="n"/>
     </row>
     <row r="751">
-      <c r="K751" s="12" t="n"/>
+      <c r="L751" s="12" t="n"/>
     </row>
     <row r="752">
-      <c r="K752" s="12" t="n"/>
+      <c r="L752" s="12" t="n"/>
     </row>
     <row r="753">
-      <c r="K753" s="12" t="n"/>
+      <c r="L753" s="12" t="n"/>
     </row>
     <row r="754">
-      <c r="K754" s="12" t="n"/>
+      <c r="L754" s="12" t="n"/>
     </row>
     <row r="755">
-      <c r="K755" s="12" t="n"/>
+      <c r="L755" s="12" t="n"/>
     </row>
     <row r="756">
-      <c r="K756" s="12" t="n"/>
+      <c r="L756" s="12" t="n"/>
     </row>
     <row r="757">
-      <c r="K757" s="12" t="n"/>
+      <c r="L757" s="12" t="n"/>
     </row>
     <row r="758">
-      <c r="K758" s="12" t="n"/>
+      <c r="L758" s="12" t="n"/>
     </row>
     <row r="759">
-      <c r="K759" s="12" t="n"/>
+      <c r="L759" s="12" t="n"/>
     </row>
     <row r="760">
-      <c r="K760" s="12" t="n"/>
+      <c r="L760" s="12" t="n"/>
     </row>
     <row r="761">
-      <c r="K761" s="12" t="n"/>
+      <c r="L761" s="12" t="n"/>
     </row>
     <row r="762">
-      <c r="K762" s="12" t="n"/>
+      <c r="L762" s="12" t="n"/>
     </row>
     <row r="763">
-      <c r="K763" s="12" t="n"/>
+      <c r="L763" s="12" t="n"/>
     </row>
     <row r="764">
-      <c r="K764" s="12" t="n"/>
+      <c r="L764" s="12" t="n"/>
     </row>
     <row r="765">
-      <c r="K765" s="12" t="n"/>
+      <c r="L765" s="12" t="n"/>
     </row>
     <row r="766">
-      <c r="K766" s="12" t="n"/>
+      <c r="L766" s="12" t="n"/>
     </row>
     <row r="767">
-      <c r="K767" s="12" t="n"/>
+      <c r="L767" s="12" t="n"/>
     </row>
     <row r="768">
-      <c r="K768" s="12" t="n"/>
+      <c r="L768" s="12" t="n"/>
     </row>
     <row r="769">
-      <c r="K769" s="12" t="n"/>
+      <c r="L769" s="12" t="n"/>
     </row>
     <row r="770">
-      <c r="K770" s="12" t="n"/>
+      <c r="L770" s="12" t="n"/>
     </row>
     <row r="771">
-      <c r="K771" s="12" t="n"/>
+      <c r="L771" s="12" t="n"/>
     </row>
     <row r="772">
-      <c r="K772" s="12" t="n"/>
+      <c r="L772" s="12" t="n"/>
     </row>
     <row r="773">
-      <c r="K773" s="12" t="n"/>
+      <c r="L773" s="12" t="n"/>
     </row>
     <row r="774">
-      <c r="K774" s="12" t="n"/>
+      <c r="L774" s="12" t="n"/>
     </row>
     <row r="775">
-      <c r="K775" s="12" t="n"/>
+      <c r="L775" s="12" t="n"/>
     </row>
     <row r="776">
-      <c r="K776" s="12" t="n"/>
+      <c r="L776" s="12" t="n"/>
     </row>
     <row r="777">
-      <c r="K777" s="12" t="n"/>
+      <c r="L777" s="12" t="n"/>
     </row>
     <row r="778">
-      <c r="K778" s="12" t="n"/>
+      <c r="L778" s="12" t="n"/>
     </row>
     <row r="779">
-      <c r="K779" s="12" t="n"/>
+      <c r="L779" s="12" t="n"/>
     </row>
     <row r="780">
-      <c r="K780" s="12" t="n"/>
+      <c r="L780" s="12" t="n"/>
     </row>
     <row r="781">
-      <c r="K781" s="12" t="n"/>
+      <c r="L781" s="12" t="n"/>
     </row>
     <row r="782">
-      <c r="K782" s="12" t="n"/>
+      <c r="L782" s="12" t="n"/>
     </row>
     <row r="783">
-      <c r="K783" s="12" t="n"/>
+      <c r="L783" s="12" t="n"/>
     </row>
     <row r="784">
-      <c r="K784" s="12" t="n"/>
+      <c r="L784" s="12" t="n"/>
     </row>
     <row r="785">
-      <c r="K785" s="12" t="n"/>
+      <c r="L785" s="12" t="n"/>
     </row>
     <row r="786">
-      <c r="K786" s="12" t="n"/>
+      <c r="L786" s="12" t="n"/>
     </row>
     <row r="787">
-      <c r="K787" s="12" t="n"/>
+      <c r="L787" s="12" t="n"/>
     </row>
     <row r="788">
-      <c r="K788" s="12" t="n"/>
+      <c r="L788" s="12" t="n"/>
     </row>
     <row r="789">
-      <c r="K789" s="12" t="n"/>
+      <c r="L789" s="12" t="n"/>
     </row>
     <row r="790">
-      <c r="K790" s="12" t="n"/>
+      <c r="L790" s="12" t="n"/>
     </row>
     <row r="791">
-      <c r="K791" s="12" t="n"/>
+      <c r="L791" s="12" t="n"/>
     </row>
     <row r="792">
-      <c r="K792" s="12" t="n"/>
+      <c r="L792" s="12" t="n"/>
     </row>
     <row r="793">
-      <c r="K793" s="12" t="n"/>
+      <c r="L793" s="12" t="n"/>
     </row>
     <row r="794">
-      <c r="K794" s="12" t="n"/>
+      <c r="L794" s="12" t="n"/>
     </row>
     <row r="795">
-      <c r="K795" s="12" t="n"/>
+      <c r="L795" s="12" t="n"/>
     </row>
     <row r="796">
-      <c r="K796" s="12" t="n"/>
+      <c r="L796" s="12" t="n"/>
     </row>
     <row r="797">
-      <c r="K797" s="12" t="n"/>
+      <c r="L797" s="12" t="n"/>
     </row>
     <row r="798">
-      <c r="K798" s="12" t="n"/>
+      <c r="L798" s="12" t="n"/>
     </row>
     <row r="799">
-      <c r="K799" s="12" t="n"/>
+      <c r="L799" s="12" t="n"/>
     </row>
     <row r="800">
-      <c r="K800" s="12" t="n"/>
+      <c r="L800" s="12" t="n"/>
     </row>
     <row r="801">
-      <c r="K801" s="12" t="n"/>
+      <c r="L801" s="12" t="n"/>
     </row>
     <row r="802">
-      <c r="K802" s="12" t="n"/>
+      <c r="L802" s="12" t="n"/>
     </row>
     <row r="803">
-      <c r="K803" s="12" t="n"/>
+      <c r="L803" s="12" t="n"/>
     </row>
     <row r="804">
-      <c r="K804" s="12" t="n"/>
+      <c r="L804" s="12" t="n"/>
     </row>
     <row r="805">
-      <c r="K805" s="12" t="n"/>
+      <c r="L805" s="12" t="n"/>
     </row>
     <row r="806">
-      <c r="K806" s="12" t="n"/>
+      <c r="L806" s="12" t="n"/>
     </row>
     <row r="807">
-      <c r="K807" s="12" t="n"/>
+      <c r="L807" s="12" t="n"/>
     </row>
     <row r="808">
-      <c r="K808" s="12" t="n"/>
+      <c r="L808" s="12" t="n"/>
     </row>
     <row r="809">
-      <c r="K809" s="12" t="n"/>
+      <c r="L809" s="12" t="n"/>
     </row>
     <row r="810">
-      <c r="K810" s="12" t="n"/>
+      <c r="L810" s="12" t="n"/>
     </row>
     <row r="811">
-      <c r="K811" s="12" t="n"/>
+      <c r="L811" s="12" t="n"/>
     </row>
     <row r="812">
-      <c r="K812" s="12" t="n"/>
+      <c r="L812" s="12" t="n"/>
     </row>
     <row r="813">
-      <c r="K813" s="12" t="n"/>
+      <c r="L813" s="12" t="n"/>
     </row>
     <row r="814">
-      <c r="K814" s="12" t="n"/>
+      <c r="L814" s="12" t="n"/>
     </row>
     <row r="815">
-      <c r="K815" s="12" t="n"/>
+      <c r="L815" s="12" t="n"/>
     </row>
     <row r="816">
-      <c r="K816" s="12" t="n"/>
+      <c r="L816" s="12" t="n"/>
     </row>
     <row r="817">
-      <c r="K817" s="12" t="n"/>
+      <c r="L817" s="12" t="n"/>
     </row>
     <row r="818">
-      <c r="K818" s="12" t="n"/>
+      <c r="L818" s="12" t="n"/>
     </row>
     <row r="819">
-      <c r="K819" s="12" t="n"/>
+      <c r="L819" s="12" t="n"/>
     </row>
     <row r="820">
-      <c r="K820" s="12" t="n"/>
+      <c r="L820" s="12" t="n"/>
     </row>
     <row r="821">
-      <c r="K821" s="12" t="n"/>
+      <c r="L821" s="12" t="n"/>
     </row>
     <row r="822">
-      <c r="K822" s="12" t="n"/>
+      <c r="L822" s="12" t="n"/>
     </row>
     <row r="823">
-      <c r="K823" s="12" t="n"/>
+      <c r="L823" s="12" t="n"/>
     </row>
     <row r="824">
-      <c r="K824" s="12" t="n"/>
+      <c r="L824" s="12" t="n"/>
     </row>
     <row r="825">
-      <c r="K825" s="12" t="n"/>
+      <c r="L825" s="12" t="n"/>
     </row>
     <row r="826">
-      <c r="K826" s="12" t="n"/>
+      <c r="L826" s="12" t="n"/>
     </row>
     <row r="827">
-      <c r="K827" s="12" t="n"/>
+      <c r="L827" s="12" t="n"/>
     </row>
     <row r="828">
-      <c r="K828" s="12" t="n"/>
+      <c r="L828" s="12" t="n"/>
     </row>
     <row r="829">
-      <c r="K829" s="12" t="n"/>
+      <c r="L829" s="12" t="n"/>
     </row>
     <row r="830">
-      <c r="K830" s="12" t="n"/>
+      <c r="L830" s="12" t="n"/>
     </row>
     <row r="831">
-      <c r="K831" s="12" t="n"/>
+      <c r="L831" s="12" t="n"/>
     </row>
     <row r="832">
-      <c r="K832" s="12" t="n"/>
+      <c r="L832" s="12" t="n"/>
     </row>
     <row r="833">
-      <c r="K833" s="12" t="n"/>
+      <c r="L833" s="12" t="n"/>
     </row>
     <row r="834">
-      <c r="K834" s="12" t="n"/>
+      <c r="L834" s="12" t="n"/>
     </row>
     <row r="835">
-      <c r="K835" s="12" t="n"/>
+      <c r="L835" s="12" t="n"/>
     </row>
     <row r="836">
-      <c r="K836" s="12" t="n"/>
+      <c r="L836" s="12" t="n"/>
     </row>
     <row r="837">
-      <c r="K837" s="12" t="n"/>
+      <c r="L837" s="12" t="n"/>
     </row>
     <row r="838">
-      <c r="K838" s="12" t="n"/>
+      <c r="L838" s="12" t="n"/>
     </row>
     <row r="839">
-      <c r="K839" s="12" t="n"/>
+      <c r="L839" s="12" t="n"/>
     </row>
     <row r="840">
-      <c r="K840" s="12" t="n"/>
+      <c r="L840" s="12" t="n"/>
     </row>
     <row r="841">
-      <c r="K841" s="12" t="n"/>
+      <c r="L841" s="12" t="n"/>
     </row>
     <row r="842">
-      <c r="K842" s="12" t="n"/>
+      <c r="L842" s="12" t="n"/>
     </row>
     <row r="843">
-      <c r="K843" s="12" t="n"/>
+      <c r="L843" s="12" t="n"/>
     </row>
     <row r="844">
-      <c r="K844" s="12" t="n"/>
+      <c r="L844" s="12" t="n"/>
     </row>
     <row r="845">
-      <c r="K845" s="12" t="n"/>
+      <c r="L845" s="12" t="n"/>
     </row>
     <row r="846">
-      <c r="K846" s="12" t="n"/>
+      <c r="L846" s="12" t="n"/>
     </row>
     <row r="847">
-      <c r="K847" s="12" t="n"/>
+      <c r="L847" s="12" t="n"/>
     </row>
     <row r="848">
-      <c r="K848" s="12" t="n"/>
+      <c r="L848" s="12" t="n"/>
     </row>
     <row r="849">
-      <c r="K849" s="12" t="n"/>
+      <c r="L849" s="12" t="n"/>
     </row>
     <row r="850">
-      <c r="K850" s="12" t="n"/>
+      <c r="L850" s="12" t="n"/>
     </row>
     <row r="851">
-      <c r="K851" s="12" t="n"/>
+      <c r="L851" s="12" t="n"/>
     </row>
     <row r="852">
-      <c r="K852" s="12" t="n"/>
+      <c r="L852" s="12" t="n"/>
     </row>
     <row r="853">
-      <c r="K853" s="12" t="n"/>
+      <c r="L853" s="12" t="n"/>
     </row>
     <row r="854">
-      <c r="K854" s="12" t="n"/>
+      <c r="L854" s="12" t="n"/>
     </row>
     <row r="855">
-      <c r="K855" s="12" t="n"/>
+      <c r="L855" s="12" t="n"/>
     </row>
     <row r="856">
-      <c r="K856" s="12" t="n"/>
+      <c r="L856" s="12" t="n"/>
     </row>
     <row r="857">
-      <c r="K857" s="12" t="n"/>
+      <c r="L857" s="12" t="n"/>
     </row>
     <row r="858">
-      <c r="K858" s="12" t="n"/>
+      <c r="L858" s="12" t="n"/>
     </row>
     <row r="859">
-      <c r="K859" s="12" t="n"/>
+      <c r="L859" s="12" t="n"/>
     </row>
     <row r="860">
-      <c r="K860" s="12" t="n"/>
+      <c r="L860" s="12" t="n"/>
     </row>
     <row r="861">
-      <c r="K861" s="12" t="n"/>
+      <c r="L861" s="12" t="n"/>
     </row>
     <row r="862">
-      <c r="K862" s="12" t="n"/>
+      <c r="L862" s="12" t="n"/>
     </row>
     <row r="863">
-      <c r="K863" s="12" t="n"/>
+      <c r="L863" s="12" t="n"/>
     </row>
     <row r="864">
-      <c r="K864" s="12" t="n"/>
+      <c r="L864" s="12" t="n"/>
     </row>
     <row r="865">
-      <c r="K865" s="12" t="n"/>
+      <c r="L865" s="12" t="n"/>
     </row>
     <row r="866">
-      <c r="K866" s="12" t="n"/>
+      <c r="L866" s="12" t="n"/>
     </row>
     <row r="867">
-      <c r="K867" s="12" t="n"/>
+      <c r="L867" s="12" t="n"/>
     </row>
     <row r="868">
-      <c r="K868" s="12" t="n"/>
+      <c r="L868" s="12" t="n"/>
     </row>
     <row r="869">
-      <c r="K869" s="12" t="n"/>
+      <c r="L869" s="12" t="n"/>
     </row>
     <row r="870">
-      <c r="K870" s="12" t="n"/>
+      <c r="L870" s="12" t="n"/>
     </row>
     <row r="871">
-      <c r="K871" s="12" t="n"/>
+      <c r="L871" s="12" t="n"/>
     </row>
     <row r="872">
-      <c r="K872" s="12" t="n"/>
+      <c r="L872" s="12" t="n"/>
     </row>
     <row r="873">
-      <c r="K873" s="12" t="n"/>
+      <c r="L873" s="12" t="n"/>
     </row>
     <row r="874">
-      <c r="K874" s="12" t="n"/>
+      <c r="L874" s="12" t="n"/>
     </row>
     <row r="875">
-      <c r="K875" s="12" t="n"/>
+      <c r="L875" s="12" t="n"/>
     </row>
     <row r="876">
-      <c r="K876" s="12" t="n"/>
+      <c r="L876" s="12" t="n"/>
     </row>
     <row r="877">
-      <c r="K877" s="12" t="n"/>
+      <c r="L877" s="12" t="n"/>
     </row>
     <row r="878">
-      <c r="K878" s="12" t="n"/>
+      <c r="L878" s="12" t="n"/>
     </row>
     <row r="879">
-      <c r="K879" s="12" t="n"/>
+      <c r="L879" s="12" t="n"/>
     </row>
     <row r="880">
-      <c r="K880" s="12" t="n"/>
+      <c r="L880" s="12" t="n"/>
     </row>
     <row r="881">
-      <c r="K881" s="12" t="n"/>
+      <c r="L881" s="12" t="n"/>
     </row>
     <row r="882">
-      <c r="K882" s="12" t="n"/>
+      <c r="L882" s="12" t="n"/>
     </row>
     <row r="883">
-      <c r="K883" s="12" t="n"/>
+      <c r="L883" s="12" t="n"/>
     </row>
     <row r="884">
-      <c r="K884" s="12" t="n"/>
+      <c r="L884" s="12" t="n"/>
     </row>
     <row r="885">
-      <c r="K885" s="12" t="n"/>
+      <c r="L885" s="12" t="n"/>
     </row>
     <row r="886">
-      <c r="K886" s="12" t="n"/>
+      <c r="L886" s="12" t="n"/>
     </row>
     <row r="887">
-      <c r="K887" s="12" t="n"/>
+      <c r="L887" s="12" t="n"/>
     </row>
     <row r="888">
-      <c r="K888" s="12" t="n"/>
+      <c r="L888" s="12" t="n"/>
     </row>
     <row r="889">
-      <c r="K889" s="12" t="n"/>
+      <c r="L889" s="12" t="n"/>
     </row>
     <row r="890">
-      <c r="K890" s="12" t="n"/>
+      <c r="L890" s="12" t="n"/>
     </row>
     <row r="891">
-      <c r="K891" s="12" t="n"/>
+      <c r="L891" s="12" t="n"/>
     </row>
     <row r="892">
-      <c r="K892" s="12" t="n"/>
+      <c r="L892" s="12" t="n"/>
     </row>
     <row r="893">
-      <c r="K893" s="12" t="n"/>
+      <c r="L893" s="12" t="n"/>
     </row>
     <row r="894">
-      <c r="K894" s="12" t="n"/>
+      <c r="L894" s="12" t="n"/>
     </row>
     <row r="895">
-      <c r="K895" s="12" t="n"/>
+      <c r="L895" s="12" t="n"/>
     </row>
     <row r="896">
-      <c r="K896" s="12" t="n"/>
+      <c r="L896" s="12" t="n"/>
     </row>
     <row r="897">
-      <c r="K897" s="12" t="n"/>
+      <c r="L897" s="12" t="n"/>
     </row>
     <row r="898">
-      <c r="K898" s="12" t="n"/>
+      <c r="L898" s="12" t="n"/>
     </row>
     <row r="899">
-      <c r="K899" s="12" t="n"/>
+      <c r="L899" s="12" t="n"/>
     </row>
     <row r="900">
-      <c r="K900" s="12" t="n"/>
+      <c r="L900" s="12" t="n"/>
     </row>
     <row r="901">
-      <c r="K901" s="12" t="n"/>
+      <c r="L901" s="12" t="n"/>
     </row>
     <row r="902">
-      <c r="K902" s="12" t="n"/>
+      <c r="L902" s="12" t="n"/>
     </row>
     <row r="903">
-      <c r="K903" s="12" t="n"/>
+      <c r="L903" s="12" t="n"/>
     </row>
     <row r="904">
-      <c r="K904" s="12" t="n"/>
+      <c r="L904" s="12" t="n"/>
     </row>
     <row r="905">
-      <c r="K905" s="12" t="n"/>
+      <c r="L905" s="12" t="n"/>
     </row>
     <row r="906">
-      <c r="K906" s="12" t="n"/>
+      <c r="L906" s="12" t="n"/>
     </row>
     <row r="907">
-      <c r="K907" s="12" t="n"/>
+      <c r="L907" s="12" t="n"/>
     </row>
     <row r="908">
-      <c r="K908" s="12" t="n"/>
+      <c r="L908" s="12" t="n"/>
     </row>
     <row r="909">
-      <c r="K909" s="12" t="n"/>
+      <c r="L909" s="12" t="n"/>
     </row>
     <row r="910">
-      <c r="K910" s="12" t="n"/>
+      <c r="L910" s="12" t="n"/>
     </row>
     <row r="911">
-      <c r="K911" s="12" t="n"/>
+      <c r="L911" s="12" t="n"/>
     </row>
     <row r="912">
-      <c r="K912" s="12" t="n"/>
+      <c r="L912" s="12" t="n"/>
     </row>
     <row r="913">
-      <c r="K913" s="12" t="n"/>
+      <c r="L913" s="12" t="n"/>
     </row>
     <row r="914">
-      <c r="K914" s="12" t="n"/>
+      <c r="L914" s="12" t="n"/>
     </row>
     <row r="915">
-      <c r="K915" s="12" t="n"/>
+      <c r="L915" s="12" t="n"/>
     </row>
     <row r="916">
-      <c r="K916" s="12" t="n"/>
+      <c r="L916" s="12" t="n"/>
     </row>
     <row r="917">
-      <c r="K917" s="12" t="n"/>
+      <c r="L917" s="12" t="n"/>
     </row>
     <row r="918">
-      <c r="K918" s="12" t="n"/>
+      <c r="L918" s="12" t="n"/>
     </row>
     <row r="919">
-      <c r="K919" s="12" t="n"/>
+      <c r="L919" s="12" t="n"/>
     </row>
     <row r="920">
-      <c r="K920" s="12" t="n"/>
+      <c r="L920" s="12" t="n"/>
     </row>
     <row r="921">
-      <c r="K921" s="12" t="n"/>
+      <c r="L921" s="12" t="n"/>
     </row>
     <row r="922">
-      <c r="K922" s="12" t="n"/>
+      <c r="L922" s="12" t="n"/>
     </row>
     <row r="923">
-      <c r="K923" s="12" t="n"/>
+      <c r="L923" s="12" t="n"/>
     </row>
     <row r="924">
-      <c r="K924" s="12" t="n"/>
+      <c r="L924" s="12" t="n"/>
     </row>
     <row r="925">
-      <c r="K925" s="12" t="n"/>
+      <c r="L925" s="12" t="n"/>
     </row>
     <row r="926">
-      <c r="K926" s="12" t="n"/>
+      <c r="L926" s="12" t="n"/>
     </row>
     <row r="927">
-      <c r="K927" s="12" t="n"/>
+      <c r="L927" s="12" t="n"/>
     </row>
     <row r="928">
-      <c r="K928" s="12" t="n"/>
+      <c r="L928" s="12" t="n"/>
     </row>
     <row r="929">
-      <c r="K929" s="12" t="n"/>
+      <c r="L929" s="12" t="n"/>
     </row>
     <row r="930">
-      <c r="K930" s="12" t="n"/>
+      <c r="L930" s="12" t="n"/>
     </row>
     <row r="931">
-      <c r="K931" s="12" t="n"/>
+      <c r="L931" s="12" t="n"/>
     </row>
     <row r="932">
-      <c r="K932" s="12" t="n"/>
+      <c r="L932" s="12" t="n"/>
     </row>
     <row r="933">
-      <c r="K933" s="12" t="n"/>
+      <c r="L933" s="12" t="n"/>
     </row>
     <row r="934">
-      <c r="K934" s="12" t="n"/>
+      <c r="L934" s="12" t="n"/>
     </row>
     <row r="935">
-      <c r="K935" s="12" t="n"/>
+      <c r="L935" s="12" t="n"/>
     </row>
     <row r="936">
-      <c r="K936" s="12" t="n"/>
+      <c r="L936" s="12" t="n"/>
     </row>
     <row r="937">
-      <c r="K937" s="12" t="n"/>
+      <c r="L937" s="12" t="n"/>
     </row>
     <row r="938">
-      <c r="K938" s="12" t="n"/>
+      <c r="L938" s="12" t="n"/>
     </row>
     <row r="939">
-      <c r="K939" s="12" t="n"/>
+      <c r="L939" s="12" t="n"/>
     </row>
     <row r="940">
-      <c r="K940" s="12" t="n"/>
+      <c r="L940" s="12" t="n"/>
     </row>
     <row r="941">
-      <c r="K941" s="12" t="n"/>
+      <c r="L941" s="12" t="n"/>
     </row>
     <row r="942">
-      <c r="K942" s="12" t="n"/>
+      <c r="L942" s="12" t="n"/>
     </row>
     <row r="943">
-      <c r="K943" s="12" t="n"/>
+      <c r="L943" s="12" t="n"/>
     </row>
     <row r="944">
-      <c r="K944" s="12" t="n"/>
+      <c r="L944" s="12" t="n"/>
     </row>
     <row r="945">
-      <c r="K945" s="12" t="n"/>
+      <c r="L945" s="12" t="n"/>
     </row>
     <row r="946">
-      <c r="K946" s="12" t="n"/>
+      <c r="L946" s="12" t="n"/>
     </row>
     <row r="947">
-      <c r="K947" s="12" t="n"/>
+      <c r="L947" s="12" t="n"/>
     </row>
     <row r="948">
-      <c r="K948" s="12" t="n"/>
+      <c r="L948" s="12" t="n"/>
     </row>
     <row r="949">
-      <c r="K949" s="12" t="n"/>
+      <c r="L949" s="12" t="n"/>
     </row>
     <row r="950">
-      <c r="K950" s="12" t="n"/>
+      <c r="L950" s="12" t="n"/>
     </row>
     <row r="951">
-      <c r="K951" s="12" t="n"/>
+      <c r="L951" s="12" t="n"/>
     </row>
     <row r="952">
-      <c r="K952" s="12" t="n"/>
+      <c r="L952" s="12" t="n"/>
     </row>
     <row r="953">
-      <c r="K953" s="12" t="n"/>
+      <c r="L953" s="12" t="n"/>
     </row>
     <row r="954">
-      <c r="K954" s="12" t="n"/>
+      <c r="L954" s="12" t="n"/>
     </row>
     <row r="955">
-      <c r="K955" s="12" t="n"/>
+      <c r="L955" s="12" t="n"/>
     </row>
     <row r="956">
-      <c r="K956" s="12" t="n"/>
+      <c r="L956" s="12" t="n"/>
     </row>
     <row r="957">
-      <c r="K957" s="12" t="n"/>
+      <c r="L957" s="12" t="n"/>
     </row>
     <row r="958">
-      <c r="K958" s="12" t="n"/>
+      <c r="L958" s="12" t="n"/>
     </row>
     <row r="959">
-      <c r="K959" s="12" t="n"/>
+      <c r="L959" s="12" t="n"/>
     </row>
     <row r="960">
-      <c r="K960" s="12" t="n"/>
+      <c r="L960" s="12" t="n"/>
     </row>
     <row r="961">
-      <c r="K961" s="12" t="n"/>
+      <c r="L961" s="12" t="n"/>
     </row>
     <row r="962">
-      <c r="K962" s="12" t="n"/>
+      <c r="L962" s="12" t="n"/>
     </row>
     <row r="963">
-      <c r="K963" s="12" t="n"/>
+      <c r="L963" s="12" t="n"/>
     </row>
     <row r="964">
-      <c r="K964" s="12" t="n"/>
+      <c r="L964" s="12" t="n"/>
     </row>
     <row r="965">
-      <c r="K965" s="12" t="n"/>
+      <c r="L965" s="12" t="n"/>
     </row>
     <row r="966">
-      <c r="K966" s="12" t="n"/>
+      <c r="L966" s="12" t="n"/>
     </row>
     <row r="967">
-      <c r="K967" s="12" t="n"/>
+      <c r="L967" s="12" t="n"/>
     </row>
     <row r="968">
-      <c r="K968" s="12" t="n"/>
+      <c r="L968" s="12" t="n"/>
     </row>
     <row r="969">
-      <c r="K969" s="12" t="n"/>
+      <c r="L969" s="12" t="n"/>
     </row>
     <row r="970">
-      <c r="K970" s="12" t="n"/>
+      <c r="L970" s="12" t="n"/>
     </row>
     <row r="971">
-      <c r="K971" s="12" t="n"/>
+      <c r="L971" s="12" t="n"/>
     </row>
     <row r="972">
-      <c r="K972" s="12" t="n"/>
+      <c r="L972" s="12" t="n"/>
     </row>
     <row r="973">
-      <c r="K973" s="12" t="n"/>
+      <c r="L973" s="12" t="n"/>
     </row>
     <row r="974">
-      <c r="K974" s="12" t="n"/>
+      <c r="L974" s="12" t="n"/>
     </row>
     <row r="975">
-      <c r="K975" s="12" t="n"/>
+      <c r="L975" s="12" t="n"/>
     </row>
     <row r="976">
-      <c r="K976" s="12" t="n"/>
+      <c r="L976" s="12" t="n"/>
     </row>
     <row r="977">
-      <c r="K977" s="12" t="n"/>
+      <c r="L977" s="12" t="n"/>
     </row>
     <row r="978">
-      <c r="K978" s="12" t="n"/>
+      <c r="L978" s="12" t="n"/>
     </row>
     <row r="979">
-      <c r="K979" s="12" t="n"/>
+      <c r="L979" s="12" t="n"/>
     </row>
     <row r="980">
-      <c r="K980" s="12" t="n"/>
+      <c r="L980" s="12" t="n"/>
     </row>
     <row r="981">
-      <c r="K981" s="12" t="n"/>
+      <c r="L981" s="12" t="n"/>
     </row>
     <row r="982">
-      <c r="K982" s="12" t="n"/>
+      <c r="L982" s="12" t="n"/>
     </row>
     <row r="983">
-      <c r="K983" s="12" t="n"/>
+      <c r="L983" s="12" t="n"/>
     </row>
     <row r="984">
-      <c r="K984" s="12" t="n"/>
+      <c r="L984" s="12" t="n"/>
     </row>
     <row r="985">
-      <c r="K985" s="12" t="n"/>
+      <c r="L985" s="12" t="n"/>
     </row>
     <row r="986">
-      <c r="K986" s="12" t="n"/>
+      <c r="L986" s="12" t="n"/>
     </row>
     <row r="987">
-      <c r="K987" s="12" t="n"/>
+      <c r="L987" s="12" t="n"/>
     </row>
     <row r="988">
-      <c r="K988" s="12" t="n"/>
+      <c r="L988" s="12" t="n"/>
     </row>
     <row r="989">
-      <c r="K989" s="12" t="n"/>
+      <c r="L989" s="12" t="n"/>
     </row>
     <row r="990">
-      <c r="K990" s="12" t="n"/>
+      <c r="L990" s="12" t="n"/>
     </row>
     <row r="991">
-      <c r="K991" s="12" t="n"/>
+      <c r="L991" s="12" t="n"/>
     </row>
     <row r="992">
-      <c r="K992" s="12" t="n"/>
+      <c r="L992" s="12" t="n"/>
     </row>
     <row r="993">
-      <c r="K993" s="12" t="n"/>
+      <c r="L993" s="12" t="n"/>
     </row>
     <row r="994">
-      <c r="K994" s="12" t="n"/>
+      <c r="L994" s="12" t="n"/>
     </row>
     <row r="995">
-      <c r="K995" s="12" t="n"/>
+      <c r="L995" s="12" t="n"/>
     </row>
     <row r="996">
-      <c r="K996" s="12" t="n"/>
+      <c r="L996" s="12" t="n"/>
     </row>
     <row r="997">
-      <c r="K997" s="12" t="n"/>
+      <c r="L997" s="12" t="n"/>
     </row>
     <row r="998">
-      <c r="K998" s="12" t="n"/>
+      <c r="L998" s="12" t="n"/>
     </row>
     <row r="999">
-      <c r="K999" s="12" t="n"/>
+      <c r="L999" s="12" t="n"/>
     </row>
     <row r="1000">
-      <c r="K1000" s="12" t="n"/>
+      <c r="L1000" s="12" t="n"/>
     </row>
     <row r="1001">
-      <c r="K1001" s="12" t="n"/>
+      <c r="L1001" s="12" t="n"/>
     </row>
     <row r="1002">
-      <c r="K1002" s="12" t="n"/>
+      <c r="L1002" s="12" t="n"/>
     </row>
     <row r="1003">
-      <c r="K1003" s="12" t="n"/>
+      <c r="L1003" s="12" t="n"/>
     </row>
     <row r="1004">
-      <c r="K1004" s="12" t="n"/>
+      <c r="L1004" s="12" t="n"/>
     </row>
     <row r="1005">
-      <c r="K1005" s="12" t="n"/>
+      <c r="L1005" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:P11"/>
-  <dataValidations count="8">
+  <autoFilter ref="A5:Q10"/>
+  <dataValidations count="9">
     <dataValidation sqref="B6:B1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Elige una opción de la lista." type="list">
       <formula1>=Listas!$A$1:$A$2</formula1>
     </dataValidation>
@@ -3984,10 +5767,10 @@
       <formula1>=Listas!$B$1:$B$2</formula1>
     </dataValidation>
     <dataValidation sqref="F6:F1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Elige una opción de la lista." type="list">
-      <formula1>=Listas!$C$1:$C$3</formula1>
+      <formula1>=Listas!$D$1:$D$2</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Elige una opción de la lista." type="list">
-      <formula1>=Listas!$A$1:$A$2</formula1>
+    <dataValidation sqref="G6:G1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Elige una opción de la lista." type="list">
+      <formula1>=Listas!$C$1:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="I6:I1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Elige una opción de la lista." type="list">
       <formula1>=Listas!$A$1:$A$2</formula1>
@@ -3995,11 +5778,14 @@
     <dataValidation sqref="J6:J1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Elige una opción de la lista." type="list">
       <formula1>=Listas!$A$1:$A$2</formula1>
     </dataValidation>
+    <dataValidation sqref="K6:K1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Elige una opción de la lista." type="list">
+      <formula1>=Listas!$A$1:$A$2</formula1>
+    </dataValidation>
     <dataValidation sqref="E6:E1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="El delta es un número (p. ej. 1, -1, 0.5)." type="decimal" operator="between">
       <formula1>-1000</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="La fecha de ejecución debe ser posterior a hoy (vacío = hoy + 3)." type="date" operator="greaterThan">
+    <dataValidation sqref="L6:L1005" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="La fecha de ejecución debe ser posterior a hoy (vacío = hoy + 3)." type="date" operator="greaterThan">
       <formula1>TODAY()</formula1>
     </dataValidation>
   </dataValidations>
@@ -4013,263 +5799,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="115" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>Qué hace cada opción</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Detalle por campo (opcional)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>ACCIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>• Rectificación: corrige la tarifa vigente; se guarda de inmediato.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo para filas con «Campos a modificar» = «Detalle en hoja Campos». Una fila por campo: «Valor nuevo» (se escribe tal cual) o «Delta» (se suma). Campo como aparece en SIRT, o ruta con « › »: bloque › campo · tabla · tabla › fila · tabla › fila › campo (ver «Qué hace cada opción»).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>• Cambio: programa una nueva versión de la tarifa para una fecha de ejecución. Solo puede haber UN cambio</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Nombre de la tarifa</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Campo (o ruta con «›»)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Valor nuevo</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Delta</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  pendiente por tarifa: si ya hay uno programado, la fila queda «No aplica» hasta que se ejecute.</t>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-010</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Datos tope descarga</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr"/>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-010</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Datos para tethering</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>DELTA (cuánto suben o bajan los números)</t>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-010</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Valor del servicio</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>-2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Vacío: +1 en rectificación y −1 en cambio. Se puede poner otro número (p. ej. 2, −1, 0.5).</t>
-        </is>
-      </c>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-010</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Minutos móvil on net › Cantidad de minutos</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Nunca baja de 0, los porcentajes no pasan de 100 y los «topes» se cambian en el orden que exige SIRT.</t>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-010</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Tecnologías y velocidades › 4G › Descarga máx. contratada</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Empaquetados que suben: el último servicio no sube (regla: suma de servicios &lt; suma de las tarifas base).</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-010</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Tecnologías y velocidades › 5G</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>CAMPOS A MODIFICAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>• Por defecto: textos (con el sello «| Rectificación/Cambio fecha hora»), valor del servicio, tarifa de</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  instalación y listas como «Tipo de Contratación».</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>• Todos los campos: además TODOS los números del paso 2 (datos, velocidades, minutos, tarifas…), «Apps sin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  consumo de datos» y los números de cada fila de las tablas (lápiz → Guardar), sin tocar tecnología, países</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ni plataformas (SIRT no permite repetirlos).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>• Solo la lista: solo los campos escritos en «Lista de campos», con su nombre como aparece en SIRT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>TABLAS Y CONDICIONALES (paso 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>• Agregar una fila a cada tabla: una fila nueva con un país / tecnología / plataforma que la tabla aún no tenga.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>• Pasar «ilimitado» a limitado: en minutos y SMS marcados como ilimitados, desmarca la casilla y llena</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  cantidad y tarifa adicional (10 y 15).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>• Cambiar canales: sube el otro Excel de canales de automatizacion/canales/ (3 ↔ 5 canales). Vacío = Sí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>CAMBIO: FECHA DE EJECUCIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Vacío: hoy + 3 días (SIRT pide al menos 2 si el cambio perjudica al usuario; hoy siempre está bloqueado).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Si el día está bloqueado en el calendario, usa el siguiente permitido (hasta 7 días).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>POR TIPO DE TARIFA</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>• Monoproductos y empaquetados: todo lo anterior (en empaquetados, en cada pestaña de servicio).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>• Licitación y Contratos (solo rectificación): además mueve inicio y fin de vigencia (+1 día, con el</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  calendario), cambia Ámbito y Moneda a la otra opción y suma el delta al Valor de contrato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>• Promociones: la rectificación / cambio de promociones aún no está grabada; esas filas quedarán en error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>REGLAS GENERALES</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>• La tarifa debe estar EN COMERCIALIZACIÓN y VIGENTE (licitaciones: vigente). Si no, «No aplica».</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>• Antes de guardar se comprueba que todos los cambios aparezcan en el resumen de SIRT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>• Solo se procesan las filas con «Ejecutar» = Sí. El Excel debe estar cerrado al correr el comando.</t>
-        </is>
-      </c>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4282,7 +5969,412 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="115" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Qué hace cada opción</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>ACCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>• Rectificación: corrige la tarifa vigente; se guarda de inmediato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>• Cambio: programa una nueva versión de la tarifa para una fecha de ejecución. Solo puede haber UN cambio</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  pendiente por tarifa: si ya hay uno programado, la fila queda «No aplica» hasta que se ejecute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>CAMBIO: SENTIDO (Beneficioso / Perjudicial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Solo en «Cambio». Separa los campos por su nombre en PRECIOS (valor del servicio, tarifa por minuto / SMS / MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>adicional, instalación, periodo de contrato) y BENEFICIOS (minutos, SMS, datos, GB, velocidades, duración,</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>decodificadores, repetidores…). Usa el valor del Delta sin signo (vacío = 1):</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>• Beneficioso para el usuario: los precios BAJAN y los beneficios SUBEN (sugerido: «Agregar una fila» = Sí).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>• Perjudicial: los precios SUBEN y los beneficios BAJAN (sugerido: «Pasar ilimitado a limitado» = Sí).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>• Vacío: el Delta se aplica igual a todos los números (como antes). En rectificación se ignora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>DELTA (cuánto suben o bajan los números)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Vacío: +1 en rectificación y −1 en cambio. Se puede poner otro número (p. ej. 2, −1, 0.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Nunca baja de 0, los porcentajes no pasan de 100 y los «topes» se cambian en el orden que exige SIRT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Empaquetados que suben: el último servicio no sube (regla: suma de servicios &lt; suma de las tarifas base).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>CAMPOS A MODIFICAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>• Por defecto: textos (con el sello «| Rectificación/Cambio fecha hora»), valor del servicio, tarifa de</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  instalación y listas como «Tipo de Contratación».</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>• Todos los campos: además TODOS los números del paso 2 (datos, velocidades, minutos, tarifas…), «Apps sin</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  consumo de datos» y los números de cada fila de las tablas (lápiz → Guardar), sin tocar tecnología, países</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ni plataformas (SIRT no permite repetirlos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>• Solo la lista: solo los campos escritos en «Lista de campos», con su nombre como aparece en SIRT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>• Detalle en hoja Campos: cada campo de la tarifa con su «Valor nuevo» o su propio «Delta» (hoja «Campos»;</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  una fila por campo, nombre como aparece en SIRT). SOLO se modifican esos campos (y los textos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  En «Campo» se puede escribir una ruta con « › » para ser más fino:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Datos tope descarga                                   → ese campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Minutos móvil on net › Cantidad de minutos            → la cantidad de ese bloque (no su tarifa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Tecnologías y velocidades                             → todos los números de todas las filas de la tabla</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Tecnologías y velocidades › 4G                        → todos los números de la fila 4G</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Tecnologías y velocidades › 4G › Descarga máx. contratada → solo esa velocidad de la fila 4G</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Tecnologías y velocidades › 3G › Tecnología  (Valor nuevo 4.5G) → cambia la tecnología de esa fila</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Tarifa minuto roaming › ALEMANIA › Tarifa              → la tarifa de la fila de Alemania</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  La «fila» es el texto de una celda de la tabla (tecnología, país, tipo…). SIRT no deja repetir tecnología ni</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  país en una tabla: el valor nuevo debe ser uno que la tabla aún no tenga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>TABLAS Y CONDICIONALES (paso 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>• Agregar una fila a cada tabla: una fila nueva con un país / tecnología / plataforma que la tabla aún no tenga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>• Pasar «ilimitado» a limitado: en minutos y SMS marcados como ilimitados, desmarca la casilla y llena</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  cantidad y tarifa adicional (10 y 15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>• Cambiar canales: sube el otro Excel de canales de automatizacion/canales/ (3 ↔ 5 canales). Vacío = Sí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>CAMBIO: FECHA DE EJECUCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Vacío: hoy + 3 días (SIRT pide al menos 2 si el cambio perjudica al usuario; hoy siempre está bloqueado).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>Si el día está bloqueado en el calendario, usa el siguiente permitido (hasta 7 días).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>POR TIPO DE TARIFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>• Monoproductos y empaquetados: todo lo anterior (en empaquetados, en cada pestaña de servicio).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>• Licitación y Contratos (solo rectificación): además mueve inicio y fin de vigencia (+1 día, con el</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  calendario), cambia Ámbito y Moneda a la otra opción y suma el delta al Valor de contrato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>• Promociones: la rectificación / cambio de promociones aún no está grabada; esas filas quedan en «Error de datos».</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>REGLAS GENERALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>• La tarifa debe estar EN COMERCIALIZACIÓN y VIGENTE (licitaciones: vigente). Si no, «No aplica».</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>• Antes de guardar se comprueba que todos los cambios aparezcan en el resumen de SIRT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>• Solo se procesan las filas con «Ejecutar» = Sí. El Excel debe estar cerrado al correr el comando.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4301,6 +6393,11 @@
           <t>Por defecto</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Beneficioso</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4318,11 +6415,23 @@
           <t>Todos los campos</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Perjudicial</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
           <t>Solo la lista</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Detalle en hoja Campos</t>
         </is>
       </c>
     </row>
